--- a/Source Data/Weight At Age/weightatageSpawningGrounds.xlsx
+++ b/Source Data/Weight At Age/weightatageSpawningGrounds.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30306"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\working\waccache\TO1PEPF00005A82\EXCELCNV\d3f0fb08-2622-444c-8a52-c7f427a1510d\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://herringscience-my.sharepoint.com/personal/tleask_herringscience_ca/Documents/Documents/GitHub/HerringScience.github.io/Source Data/Weight At Age/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{18D8F06C-38BB-4938-B3D2-1239D2F53CEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="8_{18D8F06C-38BB-4938-B3D2-1239D2F53CEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5F61872E-C6B6-4AAF-B734-6B42C2A3C4C9}"/>
   <bookViews>
-    <workbookView xWindow="-60" yWindow="-60" windowWidth="15480" windowHeight="11640" xr2:uid="{9224CDA6-B1E6-4AA2-9F09-4793D59396D4}"/>
+    <workbookView xWindow="1980" yWindow="1215" windowWidth="21600" windowHeight="11295" xr2:uid="{9224CDA6-B1E6-4AA2-9F09-4793D59396D4}"/>
   </bookViews>
   <sheets>
     <sheet name="in" sheetId="1" r:id="rId1"/>
@@ -63,7 +63,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="18">
+  <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -601,9 +601,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -641,7 +641,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -747,7 +747,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -889,7 +889,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -898,9 +898,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9685F2E5-77A6-4365-A92E-2FFD7FD63D9D}">
   <dimension ref="A1:E573"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
         <v>0</v>
       </c>
@@ -914,7 +914,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>287</v>
       </c>
@@ -931,7 +931,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>290</v>
       </c>
@@ -948,7 +948,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>291</v>
       </c>
@@ -965,7 +965,7 @@
         <v>135.690066</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>292</v>
       </c>
@@ -982,7 +982,7 @@
         <v>184.03140389999999</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>293</v>
       </c>
@@ -999,7 +999,7 @@
         <v>199.7800364</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>294</v>
       </c>
@@ -1016,7 +1016,7 @@
         <v>216.99672870000001</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>295</v>
       </c>
@@ -1033,7 +1033,7 @@
         <v>230.66498250000001</v>
       </c>
     </row>
-    <row r="9" spans="1:5">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>296</v>
       </c>
@@ -1050,7 +1050,7 @@
         <v>239.6363719</v>
       </c>
     </row>
-    <row r="10" spans="1:5">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>297</v>
       </c>
@@ -1067,7 +1067,7 @@
         <v>315.72341410000001</v>
       </c>
     </row>
-    <row r="11" spans="1:5">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>288</v>
       </c>
@@ -1084,7 +1084,7 @@
         <v>318.87601160000003</v>
       </c>
     </row>
-    <row r="12" spans="1:5">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>289</v>
       </c>
@@ -1101,7 +1101,7 @@
         <v>406.45980400000002</v>
       </c>
     </row>
-    <row r="13" spans="1:5">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>298</v>
       </c>
@@ -1118,7 +1118,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="14" spans="1:5">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>301</v>
       </c>
@@ -1135,7 +1135,7 @@
         <v>113.0421446</v>
       </c>
     </row>
-    <row r="15" spans="1:5">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>302</v>
       </c>
@@ -1152,7 +1152,7 @@
         <v>123.02631839999999</v>
       </c>
     </row>
-    <row r="16" spans="1:5">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>303</v>
       </c>
@@ -1169,7 +1169,7 @@
         <v>158.3167455</v>
       </c>
     </row>
-    <row r="17" spans="1:5">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>304</v>
       </c>
@@ -1186,7 +1186,7 @@
         <v>192.94048359999999</v>
       </c>
     </row>
-    <row r="18" spans="1:5">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>305</v>
       </c>
@@ -1203,7 +1203,7 @@
         <v>203.6644344</v>
       </c>
     </row>
-    <row r="19" spans="1:5">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>306</v>
       </c>
@@ -1220,7 +1220,7 @@
         <v>222.60715490000001</v>
       </c>
     </row>
-    <row r="20" spans="1:5">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>307</v>
       </c>
@@ -1237,7 +1237,7 @@
         <v>237.24115939999999</v>
       </c>
     </row>
-    <row r="21" spans="1:5">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>308</v>
       </c>
@@ -1254,7 +1254,7 @@
         <v>314.2558755</v>
       </c>
     </row>
-    <row r="22" spans="1:5">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>299</v>
       </c>
@@ -1271,7 +1271,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="23" spans="1:5">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>300</v>
       </c>
@@ -1288,7 +1288,7 @@
         <v>366.9185185</v>
       </c>
     </row>
-    <row r="24" spans="1:5">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>309</v>
       </c>
@@ -1305,7 +1305,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="25" spans="1:5">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>312</v>
       </c>
@@ -1322,7 +1322,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="26" spans="1:5">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>313</v>
       </c>
@@ -1339,7 +1339,7 @@
         <v>142.57819499999999</v>
       </c>
     </row>
-    <row r="27" spans="1:5">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>314</v>
       </c>
@@ -1356,7 +1356,7 @@
         <v>165.3165506</v>
       </c>
     </row>
-    <row r="28" spans="1:5">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>315</v>
       </c>
@@ -1373,7 +1373,7 @@
         <v>187.04069870000001</v>
       </c>
     </row>
-    <row r="29" spans="1:5">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>316</v>
       </c>
@@ -1390,7 +1390,7 @@
         <v>220.33861809999999</v>
       </c>
     </row>
-    <row r="30" spans="1:5">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>317</v>
       </c>
@@ -1407,7 +1407,7 @@
         <v>243.5038979</v>
       </c>
     </row>
-    <row r="31" spans="1:5">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>318</v>
       </c>
@@ -1424,7 +1424,7 @@
         <v>273.80521570000002</v>
       </c>
     </row>
-    <row r="32" spans="1:5">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>319</v>
       </c>
@@ -1441,7 +1441,7 @@
         <v>303.42665950000003</v>
       </c>
     </row>
-    <row r="33" spans="1:5">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>310</v>
       </c>
@@ -1458,7 +1458,7 @@
         <v>310.04466150000002</v>
       </c>
     </row>
-    <row r="34" spans="1:5">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>311</v>
       </c>
@@ -1475,7 +1475,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="35" spans="1:5">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>320</v>
       </c>
@@ -1492,7 +1492,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="36" spans="1:5">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>323</v>
       </c>
@@ -1509,7 +1509,7 @@
         <v>67.379144420000003</v>
       </c>
     </row>
-    <row r="37" spans="1:5">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>324</v>
       </c>
@@ -1526,7 +1526,7 @@
         <v>165.0613793</v>
       </c>
     </row>
-    <row r="38" spans="1:5">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>325</v>
       </c>
@@ -1543,7 +1543,7 @@
         <v>174.85752650000001</v>
       </c>
     </row>
-    <row r="39" spans="1:5">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>326</v>
       </c>
@@ -1560,7 +1560,7 @@
         <v>191.448789</v>
       </c>
     </row>
-    <row r="40" spans="1:5">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>327</v>
       </c>
@@ -1577,7 +1577,7 @@
         <v>212.88728829999999</v>
       </c>
     </row>
-    <row r="41" spans="1:5">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>328</v>
       </c>
@@ -1594,7 +1594,7 @@
         <v>250.8679473</v>
       </c>
     </row>
-    <row r="42" spans="1:5">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>329</v>
       </c>
@@ -1611,7 +1611,7 @@
         <v>239.9367282</v>
       </c>
     </row>
-    <row r="43" spans="1:5">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>330</v>
       </c>
@@ -1628,7 +1628,7 @@
         <v>279.97435030000003</v>
       </c>
     </row>
-    <row r="44" spans="1:5">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>321</v>
       </c>
@@ -1645,7 +1645,7 @@
         <v>279.95093960000003</v>
       </c>
     </row>
-    <row r="45" spans="1:5">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>322</v>
       </c>
@@ -1662,7 +1662,7 @@
         <v>308.70635629999998</v>
       </c>
     </row>
-    <row r="46" spans="1:5">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>331</v>
       </c>
@@ -1679,7 +1679,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="47" spans="1:5">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>334</v>
       </c>
@@ -1696,7 +1696,7 @@
         <v>105.8486209</v>
       </c>
     </row>
-    <row r="48" spans="1:5">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>335</v>
       </c>
@@ -1713,7 +1713,7 @@
         <v>116.4985781</v>
       </c>
     </row>
-    <row r="49" spans="1:5">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>336</v>
       </c>
@@ -1730,7 +1730,7 @@
         <v>153.8210962</v>
       </c>
     </row>
-    <row r="50" spans="1:5">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>337</v>
       </c>
@@ -1747,7 +1747,7 @@
         <v>182.17986389999999</v>
       </c>
     </row>
-    <row r="51" spans="1:5">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>338</v>
       </c>
@@ -1764,7 +1764,7 @@
         <v>197.7069056</v>
       </c>
     </row>
-    <row r="52" spans="1:5">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>339</v>
       </c>
@@ -1781,7 +1781,7 @@
         <v>203.30586400000001</v>
       </c>
     </row>
-    <row r="53" spans="1:5">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>340</v>
       </c>
@@ -1798,7 +1798,7 @@
         <v>241.70389449999999</v>
       </c>
     </row>
-    <row r="54" spans="1:5">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>341</v>
       </c>
@@ -1815,7 +1815,7 @@
         <v>234.02920639999999</v>
       </c>
     </row>
-    <row r="55" spans="1:5">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>332</v>
       </c>
@@ -1832,7 +1832,7 @@
         <v>233.06359269999999</v>
       </c>
     </row>
-    <row r="56" spans="1:5">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>333</v>
       </c>
@@ -1849,7 +1849,7 @@
         <v>237.23421160000001</v>
       </c>
     </row>
-    <row r="57" spans="1:5">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>342</v>
       </c>
@@ -1866,7 +1866,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="58" spans="1:5">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>345</v>
       </c>
@@ -1883,7 +1883,7 @@
         <v>65.433339309999994</v>
       </c>
     </row>
-    <row r="59" spans="1:5">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>346</v>
       </c>
@@ -1900,7 +1900,7 @@
         <v>135.02890959999999</v>
       </c>
     </row>
-    <row r="60" spans="1:5">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>347</v>
       </c>
@@ -1917,7 +1917,7 @@
         <v>153.49343260000001</v>
       </c>
     </row>
-    <row r="61" spans="1:5">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>348</v>
       </c>
@@ -1934,7 +1934,7 @@
         <v>182.524393</v>
       </c>
     </row>
-    <row r="62" spans="1:5">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>349</v>
       </c>
@@ -1951,7 +1951,7 @@
         <v>211.34542780000001</v>
       </c>
     </row>
-    <row r="63" spans="1:5">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>350</v>
       </c>
@@ -1968,7 +1968,7 @@
         <v>228.84998849999999</v>
       </c>
     </row>
-    <row r="64" spans="1:5">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>351</v>
       </c>
@@ -1985,7 +1985,7 @@
         <v>245.38126020000001</v>
       </c>
     </row>
-    <row r="65" spans="1:5">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>352</v>
       </c>
@@ -2002,7 +2002,7 @@
         <v>249.69560290000001</v>
       </c>
     </row>
-    <row r="66" spans="1:5">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>343</v>
       </c>
@@ -2019,7 +2019,7 @@
         <v>288.7027109</v>
       </c>
     </row>
-    <row r="67" spans="1:5">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>344</v>
       </c>
@@ -2036,7 +2036,7 @@
         <v>246.69970900000001</v>
       </c>
     </row>
-    <row r="68" spans="1:5">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>353</v>
       </c>
@@ -2053,7 +2053,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="69" spans="1:5">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>356</v>
       </c>
@@ -2070,7 +2070,7 @@
         <v>94.457780479999997</v>
       </c>
     </row>
-    <row r="70" spans="1:5">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>357</v>
       </c>
@@ -2087,7 +2087,7 @@
         <v>136.67038579999999</v>
       </c>
     </row>
-    <row r="71" spans="1:5">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>358</v>
       </c>
@@ -2104,7 +2104,7 @@
         <v>158.0718147</v>
       </c>
     </row>
-    <row r="72" spans="1:5">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>359</v>
       </c>
@@ -2121,7 +2121,7 @@
         <v>172.06368259999999</v>
       </c>
     </row>
-    <row r="73" spans="1:5">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>360</v>
       </c>
@@ -2138,7 +2138,7 @@
         <v>193.27429570000001</v>
       </c>
     </row>
-    <row r="74" spans="1:5">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A74">
         <v>361</v>
       </c>
@@ -2155,7 +2155,7 @@
         <v>207.66253459999999</v>
       </c>
     </row>
-    <row r="75" spans="1:5">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A75">
         <v>362</v>
       </c>
@@ -2172,7 +2172,7 @@
         <v>228.9443588</v>
       </c>
     </row>
-    <row r="76" spans="1:5">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A76">
         <v>363</v>
       </c>
@@ -2189,7 +2189,7 @@
         <v>251.4667891</v>
       </c>
     </row>
-    <row r="77" spans="1:5">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A77">
         <v>354</v>
       </c>
@@ -2206,7 +2206,7 @@
         <v>312.05350650000003</v>
       </c>
     </row>
-    <row r="78" spans="1:5">
+    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A78">
         <v>355</v>
       </c>
@@ -2223,7 +2223,7 @@
         <v>285.36718139999999</v>
       </c>
     </row>
-    <row r="79" spans="1:5">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A79">
         <v>364</v>
       </c>
@@ -2240,7 +2240,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="80" spans="1:5">
+    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A80">
         <v>367</v>
       </c>
@@ -2257,7 +2257,7 @@
         <v>62.485986259999997</v>
       </c>
     </row>
-    <row r="81" spans="1:5">
+    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A81">
         <v>368</v>
       </c>
@@ -2274,7 +2274,7 @@
         <v>99.695288360000006</v>
       </c>
     </row>
-    <row r="82" spans="1:5">
+    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A82">
         <v>369</v>
       </c>
@@ -2291,7 +2291,7 @@
         <v>172.64037279999999</v>
       </c>
     </row>
-    <row r="83" spans="1:5">
+    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A83">
         <v>370</v>
       </c>
@@ -2308,7 +2308,7 @@
         <v>196.55732459999999</v>
       </c>
     </row>
-    <row r="84" spans="1:5">
+    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A84">
         <v>371</v>
       </c>
@@ -2325,7 +2325,7 @@
         <v>201.54003610000001</v>
       </c>
     </row>
-    <row r="85" spans="1:5">
+    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A85">
         <v>372</v>
       </c>
@@ -2342,7 +2342,7 @@
         <v>218.0277203</v>
       </c>
     </row>
-    <row r="86" spans="1:5">
+    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A86">
         <v>373</v>
       </c>
@@ -2359,7 +2359,7 @@
         <v>237.04576789999999</v>
       </c>
     </row>
-    <row r="87" spans="1:5">
+    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A87">
         <v>374</v>
       </c>
@@ -2376,7 +2376,7 @@
         <v>217.66155599999999</v>
       </c>
     </row>
-    <row r="88" spans="1:5">
+    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A88">
         <v>365</v>
       </c>
@@ -2393,7 +2393,7 @@
         <v>262.99621580000002</v>
       </c>
     </row>
-    <row r="89" spans="1:5">
+    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A89">
         <v>366</v>
       </c>
@@ -2410,7 +2410,7 @@
         <v>274.68015020000001</v>
       </c>
     </row>
-    <row r="90" spans="1:5">
+    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A90">
         <v>375</v>
       </c>
@@ -2427,7 +2427,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="91" spans="1:5">
+    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A91">
         <v>378</v>
       </c>
@@ -2444,7 +2444,7 @@
         <v>100.200565</v>
       </c>
     </row>
-    <row r="92" spans="1:5">
+    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A92">
         <v>379</v>
       </c>
@@ -2461,7 +2461,7 @@
         <v>133.94273770000001</v>
       </c>
     </row>
-    <row r="93" spans="1:5">
+    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A93">
         <v>380</v>
       </c>
@@ -2478,7 +2478,7 @@
         <v>176.3307896</v>
       </c>
     </row>
-    <row r="94" spans="1:5">
+    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A94">
         <v>381</v>
       </c>
@@ -2495,7 +2495,7 @@
         <v>204.26231870000001</v>
       </c>
     </row>
-    <row r="95" spans="1:5">
+    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A95">
         <v>382</v>
       </c>
@@ -2512,7 +2512,7 @@
         <v>218.22226219999999</v>
       </c>
     </row>
-    <row r="96" spans="1:5">
+    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A96">
         <v>383</v>
       </c>
@@ -2529,7 +2529,7 @@
         <v>234.84319690000001</v>
       </c>
     </row>
-    <row r="97" spans="1:5">
+    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A97">
         <v>384</v>
       </c>
@@ -2546,7 +2546,7 @@
         <v>250.5765711</v>
       </c>
     </row>
-    <row r="98" spans="1:5">
+    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A98">
         <v>385</v>
       </c>
@@ -2563,7 +2563,7 @@
         <v>261.17252789999998</v>
       </c>
     </row>
-    <row r="99" spans="1:5">
+    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A99">
         <v>376</v>
       </c>
@@ -2580,7 +2580,7 @@
         <v>306.69589089999999</v>
       </c>
     </row>
-    <row r="100" spans="1:5">
+    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A100">
         <v>377</v>
       </c>
@@ -2597,7 +2597,7 @@
         <v>258.85167949999999</v>
       </c>
     </row>
-    <row r="101" spans="1:5">
+    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A101">
         <v>386</v>
       </c>
@@ -2614,7 +2614,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="102" spans="1:5">
+    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A102">
         <v>389</v>
       </c>
@@ -2631,7 +2631,7 @@
         <v>144.62195800000001</v>
       </c>
     </row>
-    <row r="103" spans="1:5">
+    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A103">
         <v>390</v>
       </c>
@@ -2648,7 +2648,7 @@
         <v>133.14572509999999</v>
       </c>
     </row>
-    <row r="104" spans="1:5">
+    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A104">
         <v>391</v>
       </c>
@@ -2665,7 +2665,7 @@
         <v>166.540187</v>
       </c>
     </row>
-    <row r="105" spans="1:5">
+    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A105">
         <v>392</v>
       </c>
@@ -2682,7 +2682,7 @@
         <v>196.8988358</v>
       </c>
     </row>
-    <row r="106" spans="1:5">
+    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A106">
         <v>393</v>
       </c>
@@ -2699,7 +2699,7 @@
         <v>226.9554009</v>
       </c>
     </row>
-    <row r="107" spans="1:5">
+    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A107">
         <v>394</v>
       </c>
@@ -2716,7 +2716,7 @@
         <v>239.89962389999999</v>
       </c>
     </row>
-    <row r="108" spans="1:5">
+    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A108">
         <v>395</v>
       </c>
@@ -2733,7 +2733,7 @@
         <v>261.29117839999998</v>
       </c>
     </row>
-    <row r="109" spans="1:5">
+    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A109">
         <v>396</v>
       </c>
@@ -2750,7 +2750,7 @@
         <v>267.5551365</v>
       </c>
     </row>
-    <row r="110" spans="1:5">
+    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A110">
         <v>387</v>
       </c>
@@ -2767,7 +2767,7 @@
         <v>283.199479</v>
       </c>
     </row>
-    <row r="111" spans="1:5">
+    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A111">
         <v>388</v>
       </c>
@@ -2784,7 +2784,7 @@
         <v>396.79771010000002</v>
       </c>
     </row>
-    <row r="112" spans="1:5">
+    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A112">
         <v>397</v>
       </c>
@@ -2801,7 +2801,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="113" spans="1:5">
+    <row r="113" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A113">
         <v>400</v>
       </c>
@@ -2818,7 +2818,7 @@
         <v>69.752932169999994</v>
       </c>
     </row>
-    <row r="114" spans="1:5">
+    <row r="114" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A114">
         <v>401</v>
       </c>
@@ -2835,7 +2835,7 @@
         <v>113.733324</v>
       </c>
     </row>
-    <row r="115" spans="1:5">
+    <row r="115" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A115">
         <v>402</v>
       </c>
@@ -2852,7 +2852,7 @@
         <v>150.87138049999999</v>
       </c>
     </row>
-    <row r="116" spans="1:5">
+    <row r="116" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A116">
         <v>403</v>
       </c>
@@ -2869,7 +2869,7 @@
         <v>171.53658300000001</v>
       </c>
     </row>
-    <row r="117" spans="1:5">
+    <row r="117" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A117">
         <v>404</v>
       </c>
@@ -2886,7 +2886,7 @@
         <v>220.27055480000001</v>
       </c>
     </row>
-    <row r="118" spans="1:5">
+    <row r="118" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A118">
         <v>405</v>
       </c>
@@ -2903,7 +2903,7 @@
         <v>249.87828479999999</v>
       </c>
     </row>
-    <row r="119" spans="1:5">
+    <row r="119" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A119">
         <v>406</v>
       </c>
@@ -2920,7 +2920,7 @@
         <v>273.15034370000001</v>
       </c>
     </row>
-    <row r="120" spans="1:5">
+    <row r="120" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A120">
         <v>407</v>
       </c>
@@ -2937,7 +2937,7 @@
         <v>273.91251060000002</v>
       </c>
     </row>
-    <row r="121" spans="1:5">
+    <row r="121" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A121">
         <v>398</v>
       </c>
@@ -2954,7 +2954,7 @@
         <v>293.5149644</v>
       </c>
     </row>
-    <row r="122" spans="1:5">
+    <row r="122" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A122">
         <v>399</v>
       </c>
@@ -2971,7 +2971,7 @@
         <v>386.15193249999999</v>
       </c>
     </row>
-    <row r="123" spans="1:5">
+    <row r="123" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A123">
         <v>408</v>
       </c>
@@ -2988,7 +2988,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="124" spans="1:5">
+    <row r="124" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A124">
         <v>411</v>
       </c>
@@ -3005,7 +3005,7 @@
         <v>69.796547329999996</v>
       </c>
     </row>
-    <row r="125" spans="1:5">
+    <row r="125" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A125">
         <v>412</v>
       </c>
@@ -3022,7 +3022,7 @@
         <v>113.044577</v>
       </c>
     </row>
-    <row r="126" spans="1:5">
+    <row r="126" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A126">
         <v>413</v>
       </c>
@@ -3039,7 +3039,7 @@
         <v>136.0354912</v>
       </c>
     </row>
-    <row r="127" spans="1:5">
+    <row r="127" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A127">
         <v>414</v>
       </c>
@@ -3056,7 +3056,7 @@
         <v>161.58483150000001</v>
       </c>
     </row>
-    <row r="128" spans="1:5">
+    <row r="128" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A128">
         <v>415</v>
       </c>
@@ -3073,7 +3073,7 @@
         <v>197.2616965</v>
       </c>
     </row>
-    <row r="129" spans="1:5">
+    <row r="129" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A129">
         <v>416</v>
       </c>
@@ -3090,7 +3090,7 @@
         <v>208.4074243</v>
       </c>
     </row>
-    <row r="130" spans="1:5">
+    <row r="130" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A130">
         <v>417</v>
       </c>
@@ -3107,7 +3107,7 @@
         <v>247.19434279999999</v>
       </c>
     </row>
-    <row r="131" spans="1:5">
+    <row r="131" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A131">
         <v>418</v>
       </c>
@@ -3124,7 +3124,7 @@
         <v>259.23827979999999</v>
       </c>
     </row>
-    <row r="132" spans="1:5">
+    <row r="132" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A132">
         <v>409</v>
       </c>
@@ -3141,7 +3141,7 @@
         <v>272.06279030000002</v>
       </c>
     </row>
-    <row r="133" spans="1:5">
+    <row r="133" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A133">
         <v>410</v>
       </c>
@@ -3158,7 +3158,7 @@
         <v>270.98430450000001</v>
       </c>
     </row>
-    <row r="134" spans="1:5">
+    <row r="134" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A134">
         <v>419</v>
       </c>
@@ -3175,7 +3175,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="135" spans="1:5">
+    <row r="135" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A135">
         <v>422</v>
       </c>
@@ -3192,7 +3192,7 @@
         <v>62.001570460000003</v>
       </c>
     </row>
-    <row r="136" spans="1:5">
+    <row r="136" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A136">
         <v>423</v>
       </c>
@@ -3209,7 +3209,7 @@
         <v>87.315683629999995</v>
       </c>
     </row>
-    <row r="137" spans="1:5">
+    <row r="137" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A137">
         <v>424</v>
       </c>
@@ -3226,7 +3226,7 @@
         <v>150.76901169999999</v>
       </c>
     </row>
-    <row r="138" spans="1:5">
+    <row r="138" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A138">
         <v>425</v>
       </c>
@@ -3243,7 +3243,7 @@
         <v>175.58966029999999</v>
       </c>
     </row>
-    <row r="139" spans="1:5">
+    <row r="139" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A139">
         <v>426</v>
       </c>
@@ -3260,7 +3260,7 @@
         <v>193.81286040000001</v>
       </c>
     </row>
-    <row r="140" spans="1:5">
+    <row r="140" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A140">
         <v>427</v>
       </c>
@@ -3277,7 +3277,7 @@
         <v>219.0028155</v>
       </c>
     </row>
-    <row r="141" spans="1:5">
+    <row r="141" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A141">
         <v>428</v>
       </c>
@@ -3294,7 +3294,7 @@
         <v>245.50155799999999</v>
       </c>
     </row>
-    <row r="142" spans="1:5">
+    <row r="142" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A142">
         <v>429</v>
       </c>
@@ -3311,7 +3311,7 @@
         <v>289.69991299999998</v>
       </c>
     </row>
-    <row r="143" spans="1:5">
+    <row r="143" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A143">
         <v>420</v>
       </c>
@@ -3328,7 +3328,7 @@
         <v>272.31102370000002</v>
       </c>
     </row>
-    <row r="144" spans="1:5">
+    <row r="144" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A144">
         <v>421</v>
       </c>
@@ -3345,7 +3345,7 @@
         <v>296.06621209999997</v>
       </c>
     </row>
-    <row r="145" spans="1:5">
+    <row r="145" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A145">
         <v>430</v>
       </c>
@@ -3362,7 +3362,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="146" spans="1:5">
+    <row r="146" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A146">
         <v>433</v>
       </c>
@@ -3379,7 +3379,7 @@
         <v>64.806655129999996</v>
       </c>
     </row>
-    <row r="147" spans="1:5">
+    <row r="147" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A147">
         <v>434</v>
       </c>
@@ -3396,7 +3396,7 @@
         <v>96.910877450000001</v>
       </c>
     </row>
-    <row r="148" spans="1:5">
+    <row r="148" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A148">
         <v>435</v>
       </c>
@@ -3413,7 +3413,7 @@
         <v>139.96037910000001</v>
       </c>
     </row>
-    <row r="149" spans="1:5">
+    <row r="149" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A149">
         <v>436</v>
       </c>
@@ -3430,7 +3430,7 @@
         <v>161.42008480000001</v>
       </c>
     </row>
-    <row r="150" spans="1:5">
+    <row r="150" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A150">
         <v>437</v>
       </c>
@@ -3447,7 +3447,7 @@
         <v>174.56743610000001</v>
       </c>
     </row>
-    <row r="151" spans="1:5">
+    <row r="151" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A151">
         <v>438</v>
       </c>
@@ -3464,7 +3464,7 @@
         <v>192.42679699999999</v>
       </c>
     </row>
-    <row r="152" spans="1:5">
+    <row r="152" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A152">
         <v>439</v>
       </c>
@@ -3481,7 +3481,7 @@
         <v>212.4481993</v>
       </c>
     </row>
-    <row r="153" spans="1:5">
+    <row r="153" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A153">
         <v>440</v>
       </c>
@@ -3498,7 +3498,7 @@
         <v>241.09717910000001</v>
       </c>
     </row>
-    <row r="154" spans="1:5">
+    <row r="154" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A154">
         <v>431</v>
       </c>
@@ -3515,7 +3515,7 @@
         <v>259.36985069999997</v>
       </c>
     </row>
-    <row r="155" spans="1:5">
+    <row r="155" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A155">
         <v>432</v>
       </c>
@@ -3532,7 +3532,7 @@
         <v>269.42731129999999</v>
       </c>
     </row>
-    <row r="156" spans="1:5">
+    <row r="156" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A156">
         <v>441</v>
       </c>
@@ -3549,7 +3549,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="157" spans="1:5">
+    <row r="157" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A157">
         <v>444</v>
       </c>
@@ -3566,7 +3566,7 @@
         <v>59.887737600000001</v>
       </c>
     </row>
-    <row r="158" spans="1:5">
+    <row r="158" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A158">
         <v>445</v>
       </c>
@@ -3583,7 +3583,7 @@
         <v>91.358621429999999</v>
       </c>
     </row>
-    <row r="159" spans="1:5">
+    <row r="159" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A159">
         <v>446</v>
       </c>
@@ -3600,7 +3600,7 @@
         <v>121.0427358</v>
       </c>
     </row>
-    <row r="160" spans="1:5">
+    <row r="160" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A160">
         <v>447</v>
       </c>
@@ -3617,7 +3617,7 @@
         <v>152.4871589</v>
       </c>
     </row>
-    <row r="161" spans="1:5">
+    <row r="161" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A161">
         <v>448</v>
       </c>
@@ -3634,7 +3634,7 @@
         <v>179.03172169999999</v>
       </c>
     </row>
-    <row r="162" spans="1:5">
+    <row r="162" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A162">
         <v>449</v>
       </c>
@@ -3651,7 +3651,7 @@
         <v>194.6313644</v>
       </c>
     </row>
-    <row r="163" spans="1:5">
+    <row r="163" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A163">
         <v>450</v>
       </c>
@@ -3668,7 +3668,7 @@
         <v>202.5655505</v>
       </c>
     </row>
-    <row r="164" spans="1:5">
+    <row r="164" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A164">
         <v>451</v>
       </c>
@@ -3685,7 +3685,7 @@
         <v>215.14530020000001</v>
       </c>
     </row>
-    <row r="165" spans="1:5">
+    <row r="165" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A165">
         <v>442</v>
       </c>
@@ -3702,7 +3702,7 @@
         <v>265.32466140000002</v>
       </c>
     </row>
-    <row r="166" spans="1:5">
+    <row r="166" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A166">
         <v>443</v>
       </c>
@@ -3719,7 +3719,7 @@
         <v>288.54107570000002</v>
       </c>
     </row>
-    <row r="167" spans="1:5">
+    <row r="167" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A167">
         <v>452</v>
       </c>
@@ -3736,7 +3736,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="168" spans="1:5">
+    <row r="168" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A168">
         <v>455</v>
       </c>
@@ -3753,7 +3753,7 @@
         <v>101.4475975</v>
       </c>
     </row>
-    <row r="169" spans="1:5">
+    <row r="169" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A169">
         <v>456</v>
       </c>
@@ -3770,7 +3770,7 @@
         <v>134.997895</v>
       </c>
     </row>
-    <row r="170" spans="1:5">
+    <row r="170" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A170">
         <v>457</v>
       </c>
@@ -3787,7 +3787,7 @@
         <v>151.1919542</v>
       </c>
     </row>
-    <row r="171" spans="1:5">
+    <row r="171" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A171">
         <v>458</v>
       </c>
@@ -3804,7 +3804,7 @@
         <v>173.34714650000001</v>
       </c>
     </row>
-    <row r="172" spans="1:5">
+    <row r="172" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A172">
         <v>459</v>
       </c>
@@ -3821,7 +3821,7 @@
         <v>188.43883410000001</v>
       </c>
     </row>
-    <row r="173" spans="1:5">
+    <row r="173" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A173">
         <v>460</v>
       </c>
@@ -3838,7 +3838,7 @@
         <v>200.46644449999999</v>
       </c>
     </row>
-    <row r="174" spans="1:5">
+    <row r="174" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A174">
         <v>461</v>
       </c>
@@ -3855,7 +3855,7 @@
         <v>215.3583343</v>
       </c>
     </row>
-    <row r="175" spans="1:5">
+    <row r="175" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A175">
         <v>462</v>
       </c>
@@ -3872,7 +3872,7 @@
         <v>234.3752647</v>
       </c>
     </row>
-    <row r="176" spans="1:5">
+    <row r="176" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A176">
         <v>453</v>
       </c>
@@ -3889,7 +3889,7 @@
         <v>245.50138709999999</v>
       </c>
     </row>
-    <row r="177" spans="1:5">
+    <row r="177" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A177">
         <v>454</v>
       </c>
@@ -3906,7 +3906,7 @@
         <v>287.8273069</v>
       </c>
     </row>
-    <row r="178" spans="1:5">
+    <row r="178" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A178">
         <v>463</v>
       </c>
@@ -3923,7 +3923,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="179" spans="1:5">
+    <row r="179" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A179">
         <v>466</v>
       </c>
@@ -3940,7 +3940,7 @@
         <v>67.521551220000006</v>
       </c>
     </row>
-    <row r="180" spans="1:5">
+    <row r="180" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A180">
         <v>467</v>
       </c>
@@ -3957,7 +3957,7 @@
         <v>113.86181019999999</v>
       </c>
     </row>
-    <row r="181" spans="1:5">
+    <row r="181" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A181">
         <v>468</v>
       </c>
@@ -3974,7 +3974,7 @@
         <v>156.50769879999999</v>
       </c>
     </row>
-    <row r="182" spans="1:5">
+    <row r="182" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A182">
         <v>469</v>
       </c>
@@ -3991,7 +3991,7 @@
         <v>176.8275107</v>
       </c>
     </row>
-    <row r="183" spans="1:5">
+    <row r="183" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A183">
         <v>470</v>
       </c>
@@ -4008,7 +4008,7 @@
         <v>198.45299209999999</v>
       </c>
     </row>
-    <row r="184" spans="1:5">
+    <row r="184" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A184">
         <v>471</v>
       </c>
@@ -4025,7 +4025,7 @@
         <v>205.98594019999999</v>
       </c>
     </row>
-    <row r="185" spans="1:5">
+    <row r="185" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A185">
         <v>472</v>
       </c>
@@ -4042,7 +4042,7 @@
         <v>223.90765870000001</v>
       </c>
     </row>
-    <row r="186" spans="1:5">
+    <row r="186" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A186">
         <v>473</v>
       </c>
@@ -4059,7 +4059,7 @@
         <v>216.6527873</v>
       </c>
     </row>
-    <row r="187" spans="1:5">
+    <row r="187" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A187">
         <v>464</v>
       </c>
@@ -4076,7 +4076,7 @@
         <v>264.07771880000001</v>
       </c>
     </row>
-    <row r="188" spans="1:5">
+    <row r="188" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A188">
         <v>465</v>
       </c>
@@ -4093,7 +4093,7 @@
         <v>312.42118850000003</v>
       </c>
     </row>
-    <row r="189" spans="1:5">
+    <row r="189" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A189">
         <v>474</v>
       </c>
@@ -4110,7 +4110,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="190" spans="1:5">
+    <row r="190" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A190">
         <v>477</v>
       </c>
@@ -4127,7 +4127,7 @@
         <v>31.56256758</v>
       </c>
     </row>
-    <row r="191" spans="1:5">
+    <row r="191" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A191">
         <v>478</v>
       </c>
@@ -4144,7 +4144,7 @@
         <v>106.94151410000001</v>
       </c>
     </row>
-    <row r="192" spans="1:5">
+    <row r="192" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A192">
         <v>479</v>
       </c>
@@ -4161,7 +4161,7 @@
         <v>133.73732570000001</v>
       </c>
     </row>
-    <row r="193" spans="1:5">
+    <row r="193" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A193">
         <v>480</v>
       </c>
@@ -4178,7 +4178,7 @@
         <v>180.63110159999999</v>
       </c>
     </row>
-    <row r="194" spans="1:5">
+    <row r="194" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A194">
         <v>481</v>
       </c>
@@ -4195,7 +4195,7 @@
         <v>198.0836319</v>
       </c>
     </row>
-    <row r="195" spans="1:5">
+    <row r="195" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A195">
         <v>482</v>
       </c>
@@ -4212,7 +4212,7 @@
         <v>209.71271630000001</v>
       </c>
     </row>
-    <row r="196" spans="1:5">
+    <row r="196" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A196">
         <v>483</v>
       </c>
@@ -4229,7 +4229,7 @@
         <v>216.4708272</v>
       </c>
     </row>
-    <row r="197" spans="1:5">
+    <row r="197" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A197">
         <v>484</v>
       </c>
@@ -4246,7 +4246,7 @@
         <v>229.98254919999999</v>
       </c>
     </row>
-    <row r="198" spans="1:5">
+    <row r="198" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A198">
         <v>475</v>
       </c>
@@ -4263,7 +4263,7 @@
         <v>250.72395109999999</v>
       </c>
     </row>
-    <row r="199" spans="1:5">
+    <row r="199" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A199">
         <v>476</v>
       </c>
@@ -4280,7 +4280,7 @@
         <v>347.61147519999997</v>
       </c>
     </row>
-    <row r="200" spans="1:5">
+    <row r="200" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A200">
         <v>485</v>
       </c>
@@ -4297,7 +4297,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="201" spans="1:5">
+    <row r="201" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A201">
         <v>488</v>
       </c>
@@ -4314,7 +4314,7 @@
         <v>74.491296129999995</v>
       </c>
     </row>
-    <row r="202" spans="1:5">
+    <row r="202" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A202">
         <v>489</v>
       </c>
@@ -4331,7 +4331,7 @@
         <v>110.5816792</v>
       </c>
     </row>
-    <row r="203" spans="1:5">
+    <row r="203" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A203">
         <v>490</v>
       </c>
@@ -4348,7 +4348,7 @@
         <v>128.14687180000001</v>
       </c>
     </row>
-    <row r="204" spans="1:5">
+    <row r="204" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A204">
         <v>491</v>
       </c>
@@ -4365,7 +4365,7 @@
         <v>147.6861342</v>
       </c>
     </row>
-    <row r="205" spans="1:5">
+    <row r="205" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A205">
         <v>492</v>
       </c>
@@ -4382,7 +4382,7 @@
         <v>163.03269169999999</v>
       </c>
     </row>
-    <row r="206" spans="1:5">
+    <row r="206" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A206">
         <v>493</v>
       </c>
@@ -4399,7 +4399,7 @@
         <v>191.8487016</v>
       </c>
     </row>
-    <row r="207" spans="1:5">
+    <row r="207" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A207">
         <v>494</v>
       </c>
@@ -4416,7 +4416,7 @@
         <v>204.12524049999999</v>
       </c>
     </row>
-    <row r="208" spans="1:5">
+    <row r="208" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A208">
         <v>495</v>
       </c>
@@ -4433,7 +4433,7 @@
         <v>199.54111710000001</v>
       </c>
     </row>
-    <row r="209" spans="1:5">
+    <row r="209" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A209">
         <v>486</v>
       </c>
@@ -4450,7 +4450,7 @@
         <v>227.2044027</v>
       </c>
     </row>
-    <row r="210" spans="1:5">
+    <row r="210" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A210">
         <v>487</v>
       </c>
@@ -4467,7 +4467,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="211" spans="1:5">
+    <row r="211" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A211">
         <v>496</v>
       </c>
@@ -4484,7 +4484,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="212" spans="1:5">
+    <row r="212" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A212">
         <v>499</v>
       </c>
@@ -4501,7 +4501,7 @@
         <v>94.624404299999995</v>
       </c>
     </row>
-    <row r="213" spans="1:5">
+    <row r="213" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A213">
         <v>500</v>
       </c>
@@ -4518,7 +4518,7 @@
         <v>122.5850757</v>
       </c>
     </row>
-    <row r="214" spans="1:5">
+    <row r="214" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A214">
         <v>501</v>
       </c>
@@ -4535,7 +4535,7 @@
         <v>134.20268229999999</v>
       </c>
     </row>
-    <row r="215" spans="1:5">
+    <row r="215" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A215">
         <v>502</v>
       </c>
@@ -4552,7 +4552,7 @@
         <v>146.17323490000001</v>
       </c>
     </row>
-    <row r="216" spans="1:5">
+    <row r="216" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A216">
         <v>503</v>
       </c>
@@ -4569,7 +4569,7 @@
         <v>168.21620480000001</v>
       </c>
     </row>
-    <row r="217" spans="1:5">
+    <row r="217" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A217">
         <v>504</v>
       </c>
@@ -4586,7 +4586,7 @@
         <v>186.43451010000001</v>
       </c>
     </row>
-    <row r="218" spans="1:5">
+    <row r="218" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A218">
         <v>505</v>
       </c>
@@ -4603,7 +4603,7 @@
         <v>208.4473352</v>
       </c>
     </row>
-    <row r="219" spans="1:5">
+    <row r="219" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A219">
         <v>506</v>
       </c>
@@ -4620,7 +4620,7 @@
         <v>174.8827479</v>
       </c>
     </row>
-    <row r="220" spans="1:5">
+    <row r="220" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A220">
         <v>497</v>
       </c>
@@ -4637,7 +4637,7 @@
         <v>248.14425840000001</v>
       </c>
     </row>
-    <row r="221" spans="1:5">
+    <row r="221" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A221">
         <v>498</v>
       </c>
@@ -4654,7 +4654,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="222" spans="1:5">
+    <row r="222" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A222">
         <v>507</v>
       </c>
@@ -4671,7 +4671,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="223" spans="1:5">
+    <row r="223" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A223">
         <v>510</v>
       </c>
@@ -4688,7 +4688,7 @@
         <v>65.495203720000006</v>
       </c>
     </row>
-    <row r="224" spans="1:5">
+    <row r="224" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A224">
         <v>511</v>
       </c>
@@ -4705,7 +4705,7 @@
         <v>112.91369450000001</v>
       </c>
     </row>
-    <row r="225" spans="1:5">
+    <row r="225" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A225">
         <v>512</v>
       </c>
@@ -4722,7 +4722,7 @@
         <v>135.46355170000001</v>
       </c>
     </row>
-    <row r="226" spans="1:5">
+    <row r="226" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A226">
         <v>513</v>
       </c>
@@ -4739,7 +4739,7 @@
         <v>152.88633659999999</v>
       </c>
     </row>
-    <row r="227" spans="1:5">
+    <row r="227" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A227">
         <v>514</v>
       </c>
@@ -4756,7 +4756,7 @@
         <v>167.37016750000001</v>
       </c>
     </row>
-    <row r="228" spans="1:5">
+    <row r="228" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A228">
         <v>515</v>
       </c>
@@ -4773,7 +4773,7 @@
         <v>183.12722890000001</v>
       </c>
     </row>
-    <row r="229" spans="1:5">
+    <row r="229" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A229">
         <v>516</v>
       </c>
@@ -4790,7 +4790,7 @@
         <v>201.07820910000001</v>
       </c>
     </row>
-    <row r="230" spans="1:5">
+    <row r="230" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A230">
         <v>517</v>
       </c>
@@ -4807,7 +4807,7 @@
         <v>204.16113759999999</v>
       </c>
     </row>
-    <row r="231" spans="1:5">
+    <row r="231" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A231">
         <v>508</v>
       </c>
@@ -4824,7 +4824,7 @@
         <v>219.0558916</v>
       </c>
     </row>
-    <row r="232" spans="1:5">
+    <row r="232" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A232">
         <v>509</v>
       </c>
@@ -4841,7 +4841,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="233" spans="1:5">
+    <row r="233" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A233">
         <v>518</v>
       </c>
@@ -4858,7 +4858,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="234" spans="1:5">
+    <row r="234" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A234">
         <v>521</v>
       </c>
@@ -4875,7 +4875,7 @@
         <v>82.176719419999998</v>
       </c>
     </row>
-    <row r="235" spans="1:5">
+    <row r="235" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A235">
         <v>522</v>
       </c>
@@ -4892,7 +4892,7 @@
         <v>112.57712549999999</v>
       </c>
     </row>
-    <row r="236" spans="1:5">
+    <row r="236" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A236">
         <v>523</v>
       </c>
@@ -4909,7 +4909,7 @@
         <v>151.7110854</v>
       </c>
     </row>
-    <row r="237" spans="1:5">
+    <row r="237" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A237">
         <v>524</v>
       </c>
@@ -4926,7 +4926,7 @@
         <v>175.32197769999999</v>
       </c>
     </row>
-    <row r="238" spans="1:5">
+    <row r="238" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A238">
         <v>525</v>
       </c>
@@ -4943,7 +4943,7 @@
         <v>187.4329812</v>
       </c>
     </row>
-    <row r="239" spans="1:5">
+    <row r="239" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A239">
         <v>526</v>
       </c>
@@ -4960,7 +4960,7 @@
         <v>207.60007880000001</v>
       </c>
     </row>
-    <row r="240" spans="1:5">
+    <row r="240" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A240">
         <v>527</v>
       </c>
@@ -4977,7 +4977,7 @@
         <v>223.65774060000001</v>
       </c>
     </row>
-    <row r="241" spans="1:5">
+    <row r="241" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A241">
         <v>528</v>
       </c>
@@ -4994,7 +4994,7 @@
         <v>253.58231079999999</v>
       </c>
     </row>
-    <row r="242" spans="1:5">
+    <row r="242" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A242">
         <v>519</v>
       </c>
@@ -5011,7 +5011,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="243" spans="1:5">
+    <row r="243" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A243">
         <v>520</v>
       </c>
@@ -5028,7 +5028,7 @@
         <v>309.98137259999999</v>
       </c>
     </row>
-    <row r="244" spans="1:5">
+    <row r="244" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A244">
         <v>529</v>
       </c>
@@ -5045,7 +5045,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="245" spans="1:5">
+    <row r="245" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A245">
         <v>532</v>
       </c>
@@ -5062,7 +5062,7 @@
         <v>105.1497547</v>
       </c>
     </row>
-    <row r="246" spans="1:5">
+    <row r="246" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A246">
         <v>533</v>
       </c>
@@ -5079,7 +5079,7 @@
         <v>126.5921867</v>
       </c>
     </row>
-    <row r="247" spans="1:5">
+    <row r="247" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A247">
         <v>534</v>
       </c>
@@ -5096,7 +5096,7 @@
         <v>151.8454088</v>
       </c>
     </row>
-    <row r="248" spans="1:5">
+    <row r="248" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A248">
         <v>535</v>
       </c>
@@ -5113,7 +5113,7 @@
         <v>173.57634640000001</v>
       </c>
     </row>
-    <row r="249" spans="1:5">
+    <row r="249" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A249">
         <v>536</v>
       </c>
@@ -5130,7 +5130,7 @@
         <v>202.26097999999999</v>
       </c>
     </row>
-    <row r="250" spans="1:5">
+    <row r="250" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A250">
         <v>537</v>
       </c>
@@ -5147,7 +5147,7 @@
         <v>218.44166709999999</v>
       </c>
     </row>
-    <row r="251" spans="1:5">
+    <row r="251" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A251">
         <v>538</v>
       </c>
@@ -5164,7 +5164,7 @@
         <v>236.3527761</v>
       </c>
     </row>
-    <row r="252" spans="1:5">
+    <row r="252" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A252">
         <v>539</v>
       </c>
@@ -5181,7 +5181,7 @@
         <v>239.91242539999999</v>
       </c>
     </row>
-    <row r="253" spans="1:5">
+    <row r="253" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A253">
         <v>530</v>
       </c>
@@ -5198,7 +5198,7 @@
         <v>273.10139349999997</v>
       </c>
     </row>
-    <row r="254" spans="1:5">
+    <row r="254" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A254">
         <v>531</v>
       </c>
@@ -5215,7 +5215,7 @@
         <v>253.6579389</v>
       </c>
     </row>
-    <row r="255" spans="1:5">
+    <row r="255" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A255">
         <v>540</v>
       </c>
@@ -5232,7 +5232,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="256" spans="1:5">
+    <row r="256" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A256">
         <v>543</v>
       </c>
@@ -5249,7 +5249,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="257" spans="1:5">
+    <row r="257" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A257">
         <v>544</v>
       </c>
@@ -5266,7 +5266,7 @@
         <v>126.55289449999999</v>
       </c>
     </row>
-    <row r="258" spans="1:5">
+    <row r="258" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A258">
         <v>545</v>
       </c>
@@ -5283,7 +5283,7 @@
         <v>160.453058</v>
       </c>
     </row>
-    <row r="259" spans="1:5">
+    <row r="259" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A259">
         <v>546</v>
       </c>
@@ -5300,7 +5300,7 @@
         <v>178.59510940000001</v>
       </c>
     </row>
-    <row r="260" spans="1:5">
+    <row r="260" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A260">
         <v>547</v>
       </c>
@@ -5317,7 +5317,7 @@
         <v>197.4427589</v>
       </c>
     </row>
-    <row r="261" spans="1:5">
+    <row r="261" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A261">
         <v>548</v>
       </c>
@@ -5334,7 +5334,7 @@
         <v>215.27730399999999</v>
       </c>
     </row>
-    <row r="262" spans="1:5">
+    <row r="262" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A262">
         <v>549</v>
       </c>
@@ -5351,7 +5351,7 @@
         <v>224.33258989999999</v>
       </c>
     </row>
-    <row r="263" spans="1:5">
+    <row r="263" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A263">
         <v>550</v>
       </c>
@@ -5368,7 +5368,7 @@
         <v>239.0968226</v>
       </c>
     </row>
-    <row r="264" spans="1:5">
+    <row r="264" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A264">
         <v>541</v>
       </c>
@@ -5385,7 +5385,7 @@
         <v>247.21942780000001</v>
       </c>
     </row>
-    <row r="265" spans="1:5">
+    <row r="265" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A265">
         <v>542</v>
       </c>
@@ -5402,7 +5402,7 @@
         <v>248.4019687</v>
       </c>
     </row>
-    <row r="266" spans="1:5">
+    <row r="266" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A266">
         <v>551</v>
       </c>
@@ -5419,7 +5419,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="267" spans="1:5">
+    <row r="267" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A267">
         <v>554</v>
       </c>
@@ -5436,7 +5436,7 @@
         <v>91.830953829999999</v>
       </c>
     </row>
-    <row r="268" spans="1:5">
+    <row r="268" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A268">
         <v>555</v>
       </c>
@@ -5453,7 +5453,7 @@
         <v>127.8364223</v>
       </c>
     </row>
-    <row r="269" spans="1:5">
+    <row r="269" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A269">
         <v>556</v>
       </c>
@@ -5470,7 +5470,7 @@
         <v>147.47490859999999</v>
       </c>
     </row>
-    <row r="270" spans="1:5">
+    <row r="270" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A270">
         <v>557</v>
       </c>
@@ -5487,7 +5487,7 @@
         <v>163.84388509999999</v>
       </c>
     </row>
-    <row r="271" spans="1:5">
+    <row r="271" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A271">
         <v>558</v>
       </c>
@@ -5504,7 +5504,7 @@
         <v>192.99989049999999</v>
       </c>
     </row>
-    <row r="272" spans="1:5">
+    <row r="272" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A272">
         <v>559</v>
       </c>
@@ -5521,7 +5521,7 @@
         <v>206.5529555</v>
       </c>
     </row>
-    <row r="273" spans="1:5">
+    <row r="273" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A273">
         <v>560</v>
       </c>
@@ -5538,7 +5538,7 @@
         <v>221.66809019999999</v>
       </c>
     </row>
-    <row r="274" spans="1:5">
+    <row r="274" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A274">
         <v>561</v>
       </c>
@@ -5555,7 +5555,7 @@
         <v>233.52818669999999</v>
       </c>
     </row>
-    <row r="275" spans="1:5">
+    <row r="275" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A275">
         <v>552</v>
       </c>
@@ -5572,7 +5572,7 @@
         <v>248.23435670000001</v>
       </c>
     </row>
-    <row r="276" spans="1:5">
+    <row r="276" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A276">
         <v>553</v>
       </c>
@@ -5589,7 +5589,7 @@
         <v>269.2664618</v>
       </c>
     </row>
-    <row r="277" spans="1:5">
+    <row r="277" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A277">
         <v>562</v>
       </c>
@@ -5606,7 +5606,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="278" spans="1:5">
+    <row r="278" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A278">
         <v>565</v>
       </c>
@@ -5623,7 +5623,7 @@
         <v>86.409180890000002</v>
       </c>
     </row>
-    <row r="279" spans="1:5">
+    <row r="279" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A279">
         <v>566</v>
       </c>
@@ -5640,7 +5640,7 @@
         <v>142.49997719999999</v>
       </c>
     </row>
-    <row r="280" spans="1:5">
+    <row r="280" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A280">
         <v>567</v>
       </c>
@@ -5657,7 +5657,7 @@
         <v>158.53302500000001</v>
       </c>
     </row>
-    <row r="281" spans="1:5">
+    <row r="281" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A281">
         <v>568</v>
       </c>
@@ -5674,7 +5674,7 @@
         <v>172.18653330000001</v>
       </c>
     </row>
-    <row r="282" spans="1:5">
+    <row r="282" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A282">
         <v>569</v>
       </c>
@@ -5691,7 +5691,7 @@
         <v>186.2244513</v>
       </c>
     </row>
-    <row r="283" spans="1:5">
+    <row r="283" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A283">
         <v>570</v>
       </c>
@@ -5708,7 +5708,7 @@
         <v>205.4491055</v>
       </c>
     </row>
-    <row r="284" spans="1:5">
+    <row r="284" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A284">
         <v>571</v>
       </c>
@@ -5725,7 +5725,7 @@
         <v>224.891977</v>
       </c>
     </row>
-    <row r="285" spans="1:5">
+    <row r="285" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A285">
         <v>572</v>
       </c>
@@ -5742,7 +5742,7 @@
         <v>232.86102510000001</v>
       </c>
     </row>
-    <row r="286" spans="1:5">
+    <row r="286" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A286">
         <v>563</v>
       </c>
@@ -5759,7 +5759,7 @@
         <v>226.5178707</v>
       </c>
     </row>
-    <row r="287" spans="1:5">
+    <row r="287" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A287">
         <v>564</v>
       </c>
@@ -5776,7 +5776,7 @@
         <v>291.17826400000001</v>
       </c>
     </row>
-    <row r="288" spans="1:5">
+    <row r="288" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A288">
         <v>1</v>
       </c>
@@ -5793,7 +5793,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="289" spans="1:5">
+    <row r="289" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A289">
         <v>4</v>
       </c>
@@ -5810,7 +5810,7 @@
         <v>132.7614494</v>
       </c>
     </row>
-    <row r="290" spans="1:5">
+    <row r="290" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A290">
         <v>5</v>
       </c>
@@ -5827,7 +5827,7 @@
         <v>147.7089101</v>
       </c>
     </row>
-    <row r="291" spans="1:5">
+    <row r="291" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A291">
         <v>6</v>
       </c>
@@ -5844,7 +5844,7 @@
         <v>180.84397820000001</v>
       </c>
     </row>
-    <row r="292" spans="1:5">
+    <row r="292" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A292">
         <v>7</v>
       </c>
@@ -5861,7 +5861,7 @@
         <v>218.30372080000001</v>
       </c>
     </row>
-    <row r="293" spans="1:5">
+    <row r="293" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A293">
         <v>8</v>
       </c>
@@ -5878,7 +5878,7 @@
         <v>225.1190556</v>
       </c>
     </row>
-    <row r="294" spans="1:5">
+    <row r="294" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A294">
         <v>9</v>
       </c>
@@ -5895,7 +5895,7 @@
         <v>289.73585659999998</v>
       </c>
     </row>
-    <row r="295" spans="1:5">
+    <row r="295" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A295">
         <v>10</v>
       </c>
@@ -5912,7 +5912,7 @@
         <v>251.14859039999999</v>
       </c>
     </row>
-    <row r="296" spans="1:5">
+    <row r="296" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A296">
         <v>11</v>
       </c>
@@ -5929,7 +5929,7 @@
         <v>323.77377230000002</v>
       </c>
     </row>
-    <row r="297" spans="1:5">
+    <row r="297" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A297">
         <v>2</v>
       </c>
@@ -5946,7 +5946,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="298" spans="1:5">
+    <row r="298" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A298">
         <v>3</v>
       </c>
@@ -5963,7 +5963,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="299" spans="1:5">
+    <row r="299" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A299">
         <v>12</v>
       </c>
@@ -5980,7 +5980,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="300" spans="1:5">
+    <row r="300" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A300">
         <v>15</v>
       </c>
@@ -5997,7 +5997,7 @@
         <v>125.5153859</v>
       </c>
     </row>
-    <row r="301" spans="1:5">
+    <row r="301" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A301">
         <v>16</v>
       </c>
@@ -6014,7 +6014,7 @@
         <v>136.4153317</v>
       </c>
     </row>
-    <row r="302" spans="1:5">
+    <row r="302" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A302">
         <v>17</v>
       </c>
@@ -6031,7 +6031,7 @@
         <v>165.72002130000001</v>
       </c>
     </row>
-    <row r="303" spans="1:5">
+    <row r="303" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A303">
         <v>18</v>
       </c>
@@ -6048,7 +6048,7 @@
         <v>190.56889709999999</v>
       </c>
     </row>
-    <row r="304" spans="1:5">
+    <row r="304" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A304">
         <v>19</v>
       </c>
@@ -6065,7 +6065,7 @@
         <v>228.82780450000001</v>
       </c>
     </row>
-    <row r="305" spans="1:5">
+    <row r="305" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A305">
         <v>20</v>
       </c>
@@ -6082,7 +6082,7 @@
         <v>270.08874530000003</v>
       </c>
     </row>
-    <row r="306" spans="1:5">
+    <row r="306" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A306">
         <v>21</v>
       </c>
@@ -6099,7 +6099,7 @@
         <v>279.83943670000002</v>
       </c>
     </row>
-    <row r="307" spans="1:5">
+    <row r="307" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A307">
         <v>22</v>
       </c>
@@ -6116,7 +6116,7 @@
         <v>288.67714410000002</v>
       </c>
     </row>
-    <row r="308" spans="1:5">
+    <row r="308" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A308">
         <v>13</v>
       </c>
@@ -6133,7 +6133,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="309" spans="1:5">
+    <row r="309" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A309">
         <v>14</v>
       </c>
@@ -6150,7 +6150,7 @@
         <v>376.93014440000002</v>
       </c>
     </row>
-    <row r="310" spans="1:5">
+    <row r="310" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A310">
         <v>23</v>
       </c>
@@ -6167,7 +6167,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="311" spans="1:5">
+    <row r="311" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A311">
         <v>26</v>
       </c>
@@ -6184,7 +6184,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="312" spans="1:5">
+    <row r="312" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A312">
         <v>27</v>
       </c>
@@ -6201,7 +6201,7 @@
         <v>136.80129500000001</v>
       </c>
     </row>
-    <row r="313" spans="1:5">
+    <row r="313" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A313">
         <v>28</v>
       </c>
@@ -6218,7 +6218,7 @@
         <v>156.44665380000001</v>
       </c>
     </row>
-    <row r="314" spans="1:5">
+    <row r="314" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A314">
         <v>29</v>
       </c>
@@ -6235,7 +6235,7 @@
         <v>182.63953140000001</v>
       </c>
     </row>
-    <row r="315" spans="1:5">
+    <row r="315" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A315">
         <v>30</v>
       </c>
@@ -6252,7 +6252,7 @@
         <v>223.16216120000001</v>
       </c>
     </row>
-    <row r="316" spans="1:5">
+    <row r="316" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A316">
         <v>31</v>
       </c>
@@ -6269,7 +6269,7 @@
         <v>233.30008179999999</v>
       </c>
     </row>
-    <row r="317" spans="1:5">
+    <row r="317" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A317">
         <v>32</v>
       </c>
@@ -6286,7 +6286,7 @@
         <v>280.5536808</v>
       </c>
     </row>
-    <row r="318" spans="1:5">
+    <row r="318" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A318">
         <v>33</v>
       </c>
@@ -6303,7 +6303,7 @@
         <v>292.92373739999999</v>
       </c>
     </row>
-    <row r="319" spans="1:5">
+    <row r="319" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A319">
         <v>24</v>
       </c>
@@ -6320,7 +6320,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="320" spans="1:5">
+    <row r="320" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A320">
         <v>25</v>
       </c>
@@ -6337,7 +6337,7 @@
         <v>375.79049300000003</v>
       </c>
     </row>
-    <row r="321" spans="1:5">
+    <row r="321" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A321">
         <v>34</v>
       </c>
@@ -6354,7 +6354,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="322" spans="1:5">
+    <row r="322" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A322">
         <v>37</v>
       </c>
@@ -6371,7 +6371,7 @@
         <v>87.014626930000006</v>
       </c>
     </row>
-    <row r="323" spans="1:5">
+    <row r="323" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A323">
         <v>38</v>
       </c>
@@ -6388,7 +6388,7 @@
         <v>169.52530419999999</v>
       </c>
     </row>
-    <row r="324" spans="1:5">
+    <row r="324" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A324">
         <v>39</v>
       </c>
@@ -6405,7 +6405,7 @@
         <v>167.11585400000001</v>
       </c>
     </row>
-    <row r="325" spans="1:5">
+    <row r="325" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A325">
         <v>40</v>
       </c>
@@ -6422,7 +6422,7 @@
         <v>187.1760677</v>
       </c>
     </row>
-    <row r="326" spans="1:5">
+    <row r="326" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A326">
         <v>41</v>
       </c>
@@ -6439,7 +6439,7 @@
         <v>220.60933030000001</v>
       </c>
     </row>
-    <row r="327" spans="1:5">
+    <row r="327" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A327">
         <v>42</v>
       </c>
@@ -6456,7 +6456,7 @@
         <v>235.89291639999999</v>
       </c>
     </row>
-    <row r="328" spans="1:5">
+    <row r="328" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A328">
         <v>43</v>
       </c>
@@ -6473,7 +6473,7 @@
         <v>264.7692199</v>
       </c>
     </row>
-    <row r="329" spans="1:5">
+    <row r="329" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A329">
         <v>44</v>
       </c>
@@ -6490,7 +6490,7 @@
         <v>303.75887080000001</v>
       </c>
     </row>
-    <row r="330" spans="1:5">
+    <row r="330" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A330">
         <v>35</v>
       </c>
@@ -6507,7 +6507,7 @@
         <v>271.48178050000001</v>
       </c>
     </row>
-    <row r="331" spans="1:5">
+    <row r="331" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A331">
         <v>36</v>
       </c>
@@ -6524,7 +6524,7 @@
         <v>268.35769160000001</v>
       </c>
     </row>
-    <row r="332" spans="1:5">
+    <row r="332" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A332">
         <v>45</v>
       </c>
@@ -6541,7 +6541,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="333" spans="1:5">
+    <row r="333" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A333">
         <v>48</v>
       </c>
@@ -6558,7 +6558,7 @@
         <v>82.318706199999994</v>
       </c>
     </row>
-    <row r="334" spans="1:5">
+    <row r="334" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A334">
         <v>49</v>
       </c>
@@ -6575,7 +6575,7 @@
         <v>119.4330246</v>
       </c>
     </row>
-    <row r="335" spans="1:5">
+    <row r="335" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A335">
         <v>50</v>
       </c>
@@ -6592,7 +6592,7 @@
         <v>168.83711149999999</v>
       </c>
     </row>
-    <row r="336" spans="1:5">
+    <row r="336" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A336">
         <v>51</v>
       </c>
@@ -6609,7 +6609,7 @@
         <v>193.4294941</v>
       </c>
     </row>
-    <row r="337" spans="1:5">
+    <row r="337" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A337">
         <v>52</v>
       </c>
@@ -6626,7 +6626,7 @@
         <v>209.5438379</v>
       </c>
     </row>
-    <row r="338" spans="1:5">
+    <row r="338" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A338">
         <v>53</v>
       </c>
@@ -6643,7 +6643,7 @@
         <v>227.72619320000001</v>
       </c>
     </row>
-    <row r="339" spans="1:5">
+    <row r="339" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A339">
         <v>54</v>
       </c>
@@ -6660,7 +6660,7 @@
         <v>257.00882050000001</v>
       </c>
     </row>
-    <row r="340" spans="1:5">
+    <row r="340" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A340">
         <v>55</v>
       </c>
@@ -6677,7 +6677,7 @@
         <v>280.21320209999999</v>
       </c>
     </row>
-    <row r="341" spans="1:5">
+    <row r="341" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A341">
         <v>46</v>
       </c>
@@ -6694,7 +6694,7 @@
         <v>288.5623051</v>
       </c>
     </row>
-    <row r="342" spans="1:5">
+    <row r="342" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A342">
         <v>47</v>
       </c>
@@ -6711,7 +6711,7 @@
         <v>359.85580479999999</v>
       </c>
     </row>
-    <row r="343" spans="1:5">
+    <row r="343" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A343">
         <v>56</v>
       </c>
@@ -6728,7 +6728,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="344" spans="1:5">
+    <row r="344" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A344">
         <v>59</v>
       </c>
@@ -6745,7 +6745,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="345" spans="1:5">
+    <row r="345" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A345">
         <v>60</v>
       </c>
@@ -6762,7 +6762,7 @@
         <v>123.8124425</v>
       </c>
     </row>
-    <row r="346" spans="1:5">
+    <row r="346" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A346">
         <v>61</v>
       </c>
@@ -6779,7 +6779,7 @@
         <v>147.5818735</v>
       </c>
     </row>
-    <row r="347" spans="1:5">
+    <row r="347" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A347">
         <v>62</v>
       </c>
@@ -6796,7 +6796,7 @@
         <v>188.58996590000001</v>
       </c>
     </row>
-    <row r="348" spans="1:5">
+    <row r="348" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A348">
         <v>63</v>
       </c>
@@ -6813,7 +6813,7 @@
         <v>220.56015970000001</v>
       </c>
     </row>
-    <row r="349" spans="1:5">
+    <row r="349" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A349">
         <v>64</v>
       </c>
@@ -6830,7 +6830,7 @@
         <v>241.4213029</v>
       </c>
     </row>
-    <row r="350" spans="1:5">
+    <row r="350" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A350">
         <v>65</v>
       </c>
@@ -6847,7 +6847,7 @@
         <v>250.99960759999999</v>
       </c>
     </row>
-    <row r="351" spans="1:5">
+    <row r="351" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A351">
         <v>66</v>
       </c>
@@ -6864,7 +6864,7 @@
         <v>328.44077249999998</v>
       </c>
     </row>
-    <row r="352" spans="1:5">
+    <row r="352" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A352">
         <v>57</v>
       </c>
@@ -6881,7 +6881,7 @@
         <v>247.47494029999999</v>
       </c>
     </row>
-    <row r="353" spans="1:5">
+    <row r="353" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A353">
         <v>58</v>
       </c>
@@ -6898,7 +6898,7 @@
         <v>289.53130060000001</v>
       </c>
     </row>
-    <row r="354" spans="1:5">
+    <row r="354" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A354">
         <v>67</v>
       </c>
@@ -6915,7 +6915,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="355" spans="1:5">
+    <row r="355" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A355">
         <v>70</v>
       </c>
@@ -6932,7 +6932,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="356" spans="1:5">
+    <row r="356" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A356">
         <v>71</v>
       </c>
@@ -6949,7 +6949,7 @@
         <v>131.4930142</v>
       </c>
     </row>
-    <row r="357" spans="1:5">
+    <row r="357" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A357">
         <v>72</v>
       </c>
@@ -6966,7 +6966,7 @@
         <v>147.38824589999999</v>
       </c>
     </row>
-    <row r="358" spans="1:5">
+    <row r="358" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A358">
         <v>73</v>
       </c>
@@ -6983,7 +6983,7 @@
         <v>165.42135669999999</v>
       </c>
     </row>
-    <row r="359" spans="1:5">
+    <row r="359" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A359">
         <v>74</v>
       </c>
@@ -7000,7 +7000,7 @@
         <v>197.29685509999999</v>
       </c>
     </row>
-    <row r="360" spans="1:5">
+    <row r="360" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A360">
         <v>75</v>
       </c>
@@ -7017,7 +7017,7 @@
         <v>221.6544303</v>
       </c>
     </row>
-    <row r="361" spans="1:5">
+    <row r="361" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A361">
         <v>76</v>
       </c>
@@ -7034,7 +7034,7 @@
         <v>238.22264970000001</v>
       </c>
     </row>
-    <row r="362" spans="1:5">
+    <row r="362" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A362">
         <v>77</v>
       </c>
@@ -7051,7 +7051,7 @@
         <v>254.51912849999999</v>
       </c>
     </row>
-    <row r="363" spans="1:5">
+    <row r="363" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A363">
         <v>68</v>
       </c>
@@ -7068,7 +7068,7 @@
         <v>283.48832909999999</v>
       </c>
     </row>
-    <row r="364" spans="1:5">
+    <row r="364" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A364">
         <v>69</v>
       </c>
@@ -7085,7 +7085,7 @@
         <v>313.50621180000002</v>
       </c>
     </row>
-    <row r="365" spans="1:5">
+    <row r="365" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A365">
         <v>78</v>
       </c>
@@ -7102,7 +7102,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="366" spans="1:5">
+    <row r="366" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A366">
         <v>81</v>
       </c>
@@ -7119,7 +7119,7 @@
         <v>98.409998079999994</v>
       </c>
     </row>
-    <row r="367" spans="1:5">
+    <row r="367" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A367">
         <v>82</v>
       </c>
@@ -7136,7 +7136,7 @@
         <v>156.6353512</v>
       </c>
     </row>
-    <row r="368" spans="1:5">
+    <row r="368" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A368">
         <v>83</v>
       </c>
@@ -7153,7 +7153,7 @@
         <v>171.2168235</v>
       </c>
     </row>
-    <row r="369" spans="1:5">
+    <row r="369" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A369">
         <v>84</v>
       </c>
@@ -7170,7 +7170,7 @@
         <v>185.87852079999999</v>
       </c>
     </row>
-    <row r="370" spans="1:5">
+    <row r="370" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A370">
         <v>85</v>
       </c>
@@ -7187,7 +7187,7 @@
         <v>190.05842999999999</v>
       </c>
     </row>
-    <row r="371" spans="1:5">
+    <row r="371" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A371">
         <v>86</v>
       </c>
@@ -7204,7 +7204,7 @@
         <v>205.58035050000001</v>
       </c>
     </row>
-    <row r="372" spans="1:5">
+    <row r="372" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A372">
         <v>87</v>
       </c>
@@ -7221,7 +7221,7 @@
         <v>200.3762816</v>
       </c>
     </row>
-    <row r="373" spans="1:5">
+    <row r="373" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A373">
         <v>88</v>
       </c>
@@ -7238,7 +7238,7 @@
         <v>252.71074179999999</v>
       </c>
     </row>
-    <row r="374" spans="1:5">
+    <row r="374" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A374">
         <v>79</v>
       </c>
@@ -7255,7 +7255,7 @@
         <v>224.89663110000001</v>
       </c>
     </row>
-    <row r="375" spans="1:5">
+    <row r="375" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A375">
         <v>80</v>
       </c>
@@ -7272,7 +7272,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="376" spans="1:5">
+    <row r="376" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A376">
         <v>89</v>
       </c>
@@ -7289,7 +7289,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="377" spans="1:5">
+    <row r="377" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A377">
         <v>92</v>
       </c>
@@ -7306,7 +7306,7 @@
         <v>91.611669090000007</v>
       </c>
     </row>
-    <row r="378" spans="1:5">
+    <row r="378" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A378">
         <v>93</v>
       </c>
@@ -7323,7 +7323,7 @@
         <v>124.0363949</v>
       </c>
     </row>
-    <row r="379" spans="1:5">
+    <row r="379" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A379">
         <v>94</v>
       </c>
@@ -7340,7 +7340,7 @@
         <v>157.2495807</v>
       </c>
     </row>
-    <row r="380" spans="1:5">
+    <row r="380" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A380">
         <v>95</v>
       </c>
@@ -7357,7 +7357,7 @@
         <v>192.78885289999999</v>
       </c>
     </row>
-    <row r="381" spans="1:5">
+    <row r="381" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A381">
         <v>96</v>
       </c>
@@ -7374,7 +7374,7 @@
         <v>218.0398873</v>
       </c>
     </row>
-    <row r="382" spans="1:5">
+    <row r="382" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A382">
         <v>97</v>
       </c>
@@ -7391,7 +7391,7 @@
         <v>235.70506829999999</v>
       </c>
     </row>
-    <row r="383" spans="1:5">
+    <row r="383" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A383">
         <v>98</v>
       </c>
@@ -7408,7 +7408,7 @@
         <v>276.0548728</v>
       </c>
     </row>
-    <row r="384" spans="1:5">
+    <row r="384" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A384">
         <v>99</v>
       </c>
@@ -7425,7 +7425,7 @@
         <v>287.11950230000002</v>
       </c>
     </row>
-    <row r="385" spans="1:5">
+    <row r="385" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A385">
         <v>90</v>
       </c>
@@ -7442,7 +7442,7 @@
         <v>265.68307650000003</v>
       </c>
     </row>
-    <row r="386" spans="1:5">
+    <row r="386" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A386">
         <v>91</v>
       </c>
@@ -7459,7 +7459,7 @@
         <v>451.15947180000001</v>
       </c>
     </row>
-    <row r="387" spans="1:5">
+    <row r="387" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A387">
         <v>100</v>
       </c>
@@ -7476,7 +7476,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="388" spans="1:5">
+    <row r="388" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A388">
         <v>103</v>
       </c>
@@ -7493,7 +7493,7 @@
         <v>90.048437230000005</v>
       </c>
     </row>
-    <row r="389" spans="1:5">
+    <row r="389" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A389">
         <v>104</v>
       </c>
@@ -7510,7 +7510,7 @@
         <v>134.42028389999999</v>
       </c>
     </row>
-    <row r="390" spans="1:5">
+    <row r="390" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A390">
         <v>105</v>
       </c>
@@ -7527,7 +7527,7 @@
         <v>162.30368920000001</v>
       </c>
     </row>
-    <row r="391" spans="1:5">
+    <row r="391" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A391">
         <v>106</v>
       </c>
@@ -7544,7 +7544,7 @@
         <v>192.99238080000001</v>
       </c>
     </row>
-    <row r="392" spans="1:5">
+    <row r="392" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A392">
         <v>107</v>
       </c>
@@ -7561,7 +7561,7 @@
         <v>230.20493619999999</v>
       </c>
     </row>
-    <row r="393" spans="1:5">
+    <row r="393" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A393">
         <v>108</v>
       </c>
@@ -7578,7 +7578,7 @@
         <v>234.4727072</v>
       </c>
     </row>
-    <row r="394" spans="1:5">
+    <row r="394" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A394">
         <v>109</v>
       </c>
@@ -7595,7 +7595,7 @@
         <v>255.5666129</v>
       </c>
     </row>
-    <row r="395" spans="1:5">
+    <row r="395" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A395">
         <v>110</v>
       </c>
@@ -7612,7 +7612,7 @@
         <v>275.94381379999999</v>
       </c>
     </row>
-    <row r="396" spans="1:5">
+    <row r="396" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A396">
         <v>101</v>
       </c>
@@ -7629,7 +7629,7 @@
         <v>352.46174239999999</v>
       </c>
     </row>
-    <row r="397" spans="1:5">
+    <row r="397" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A397">
         <v>102</v>
       </c>
@@ -7646,7 +7646,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="398" spans="1:5">
+    <row r="398" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A398">
         <v>111</v>
       </c>
@@ -7663,7 +7663,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="399" spans="1:5">
+    <row r="399" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A399">
         <v>114</v>
       </c>
@@ -7680,7 +7680,7 @@
         <v>66.889728989999995</v>
       </c>
     </row>
-    <row r="400" spans="1:5">
+    <row r="400" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A400">
         <v>115</v>
       </c>
@@ -7697,7 +7697,7 @@
         <v>130.98184119999999</v>
       </c>
     </row>
-    <row r="401" spans="1:5">
+    <row r="401" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A401">
         <v>116</v>
       </c>
@@ -7714,7 +7714,7 @@
         <v>148.08106979999999</v>
       </c>
     </row>
-    <row r="402" spans="1:5">
+    <row r="402" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A402">
         <v>117</v>
       </c>
@@ -7731,7 +7731,7 @@
         <v>182.0539982</v>
       </c>
     </row>
-    <row r="403" spans="1:5">
+    <row r="403" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A403">
         <v>118</v>
       </c>
@@ -7748,7 +7748,7 @@
         <v>218.31181230000001</v>
       </c>
     </row>
-    <row r="404" spans="1:5">
+    <row r="404" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A404">
         <v>119</v>
       </c>
@@ -7765,7 +7765,7 @@
         <v>231.8861958</v>
       </c>
     </row>
-    <row r="405" spans="1:5">
+    <row r="405" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A405">
         <v>120</v>
       </c>
@@ -7782,7 +7782,7 @@
         <v>254.3660045</v>
       </c>
     </row>
-    <row r="406" spans="1:5">
+    <row r="406" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A406">
         <v>121</v>
       </c>
@@ -7799,7 +7799,7 @@
         <v>269.12504209999997</v>
       </c>
     </row>
-    <row r="407" spans="1:5">
+    <row r="407" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A407">
         <v>112</v>
       </c>
@@ -7816,7 +7816,7 @@
         <v>270.67779469999999</v>
       </c>
     </row>
-    <row r="408" spans="1:5">
+    <row r="408" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A408">
         <v>113</v>
       </c>
@@ -7833,7 +7833,7 @@
         <v>350.97691409999999</v>
       </c>
     </row>
-    <row r="409" spans="1:5">
+    <row r="409" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A409">
         <v>122</v>
       </c>
@@ -7850,7 +7850,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="410" spans="1:5">
+    <row r="410" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A410">
         <v>125</v>
       </c>
@@ -7867,7 +7867,7 @@
         <v>59.388477770000001</v>
       </c>
     </row>
-    <row r="411" spans="1:5">
+    <row r="411" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A411">
         <v>126</v>
       </c>
@@ -7884,7 +7884,7 @@
         <v>103.19593450000001</v>
       </c>
     </row>
-    <row r="412" spans="1:5">
+    <row r="412" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A412">
         <v>127</v>
       </c>
@@ -7901,7 +7901,7 @@
         <v>123.90655080000001</v>
       </c>
     </row>
-    <row r="413" spans="1:5">
+    <row r="413" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A413">
         <v>128</v>
       </c>
@@ -7918,7 +7918,7 @@
         <v>151.33955159999999</v>
       </c>
     </row>
-    <row r="414" spans="1:5">
+    <row r="414" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A414">
         <v>129</v>
       </c>
@@ -7935,7 +7935,7 @@
         <v>159.90268470000001</v>
       </c>
     </row>
-    <row r="415" spans="1:5">
+    <row r="415" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A415">
         <v>130</v>
       </c>
@@ -7952,7 +7952,7 @@
         <v>206.56285370000001</v>
       </c>
     </row>
-    <row r="416" spans="1:5">
+    <row r="416" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A416">
         <v>131</v>
       </c>
@@ -7969,7 +7969,7 @@
         <v>236.1133064</v>
       </c>
     </row>
-    <row r="417" spans="1:5">
+    <row r="417" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A417">
         <v>132</v>
       </c>
@@ -7986,7 +7986,7 @@
         <v>240.91866479999999</v>
       </c>
     </row>
-    <row r="418" spans="1:5">
+    <row r="418" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A418">
         <v>123</v>
       </c>
@@ -8003,7 +8003,7 @@
         <v>242.7521644</v>
       </c>
     </row>
-    <row r="419" spans="1:5">
+    <row r="419" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A419">
         <v>124</v>
       </c>
@@ -8020,7 +8020,7 @@
         <v>249.08265220000001</v>
       </c>
     </row>
-    <row r="420" spans="1:5">
+    <row r="420" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A420">
         <v>133</v>
       </c>
@@ -8037,7 +8037,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="421" spans="1:5">
+    <row r="421" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A421">
         <v>136</v>
       </c>
@@ -8054,7 +8054,7 @@
         <v>64.095860590000001</v>
       </c>
     </row>
-    <row r="422" spans="1:5">
+    <row r="422" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A422">
         <v>137</v>
       </c>
@@ -8071,7 +8071,7 @@
         <v>115.4741748</v>
       </c>
     </row>
-    <row r="423" spans="1:5">
+    <row r="423" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A423">
         <v>138</v>
       </c>
@@ -8088,7 +8088,7 @@
         <v>132.71230030000001</v>
       </c>
     </row>
-    <row r="424" spans="1:5">
+    <row r="424" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A424">
         <v>139</v>
       </c>
@@ -8105,7 +8105,7 @@
         <v>145.7194552</v>
       </c>
     </row>
-    <row r="425" spans="1:5">
+    <row r="425" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A425">
         <v>140</v>
       </c>
@@ -8122,7 +8122,7 @@
         <v>164.19403209999999</v>
       </c>
     </row>
-    <row r="426" spans="1:5">
+    <row r="426" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A426">
         <v>141</v>
       </c>
@@ -8139,7 +8139,7 @@
         <v>174.610536</v>
       </c>
     </row>
-    <row r="427" spans="1:5">
+    <row r="427" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A427">
         <v>142</v>
       </c>
@@ -8156,7 +8156,7 @@
         <v>231.07431070000001</v>
       </c>
     </row>
-    <row r="428" spans="1:5">
+    <row r="428" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A428">
         <v>143</v>
       </c>
@@ -8173,7 +8173,7 @@
         <v>229.25968</v>
       </c>
     </row>
-    <row r="429" spans="1:5">
+    <row r="429" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A429">
         <v>134</v>
       </c>
@@ -8190,7 +8190,7 @@
         <v>241.28573209999999</v>
       </c>
     </row>
-    <row r="430" spans="1:5">
+    <row r="430" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A430">
         <v>135</v>
       </c>
@@ -8207,7 +8207,7 @@
         <v>293.39493279999999</v>
       </c>
     </row>
-    <row r="431" spans="1:5">
+    <row r="431" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A431">
         <v>144</v>
       </c>
@@ -8224,7 +8224,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="432" spans="1:5">
+    <row r="432" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A432">
         <v>147</v>
       </c>
@@ -8241,7 +8241,7 @@
         <v>63.365702249999998</v>
       </c>
     </row>
-    <row r="433" spans="1:5">
+    <row r="433" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A433">
         <v>148</v>
       </c>
@@ -8258,7 +8258,7 @@
         <v>109.0666877</v>
       </c>
     </row>
-    <row r="434" spans="1:5">
+    <row r="434" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A434">
         <v>149</v>
       </c>
@@ -8275,7 +8275,7 @@
         <v>136.64298579999999</v>
       </c>
     </row>
-    <row r="435" spans="1:5">
+    <row r="435" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A435">
         <v>150</v>
       </c>
@@ -8292,7 +8292,7 @@
         <v>156.24998919999999</v>
       </c>
     </row>
-    <row r="436" spans="1:5">
+    <row r="436" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A436">
         <v>151</v>
       </c>
@@ -8309,7 +8309,7 @@
         <v>171.7330135</v>
       </c>
     </row>
-    <row r="437" spans="1:5">
+    <row r="437" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A437">
         <v>152</v>
       </c>
@@ -8326,7 +8326,7 @@
         <v>179.21094540000001</v>
       </c>
     </row>
-    <row r="438" spans="1:5">
+    <row r="438" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A438">
         <v>153</v>
       </c>
@@ -8343,7 +8343,7 @@
         <v>203.1574938</v>
       </c>
     </row>
-    <row r="439" spans="1:5">
+    <row r="439" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A439">
         <v>154</v>
       </c>
@@ -8360,7 +8360,7 @@
         <v>238.00376080000001</v>
       </c>
     </row>
-    <row r="440" spans="1:5">
+    <row r="440" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A440">
         <v>145</v>
       </c>
@@ -8377,7 +8377,7 @@
         <v>258.371622</v>
       </c>
     </row>
-    <row r="441" spans="1:5">
+    <row r="441" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A441">
         <v>146</v>
       </c>
@@ -8394,7 +8394,7 @@
         <v>296.26377179999997</v>
       </c>
     </row>
-    <row r="442" spans="1:5">
+    <row r="442" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A442">
         <v>155</v>
       </c>
@@ -8411,7 +8411,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="443" spans="1:5">
+    <row r="443" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A443">
         <v>158</v>
       </c>
@@ -8428,7 +8428,7 @@
         <v>88.607096209999995</v>
       </c>
     </row>
-    <row r="444" spans="1:5">
+    <row r="444" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A444">
         <v>159</v>
       </c>
@@ -8445,7 +8445,7 @@
         <v>121.15373769999999</v>
       </c>
     </row>
-    <row r="445" spans="1:5">
+    <row r="445" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A445">
         <v>160</v>
       </c>
@@ -8462,7 +8462,7 @@
         <v>135.8358408</v>
       </c>
     </row>
-    <row r="446" spans="1:5">
+    <row r="446" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A446">
         <v>161</v>
       </c>
@@ -8479,7 +8479,7 @@
         <v>166.89888970000001</v>
       </c>
     </row>
-    <row r="447" spans="1:5">
+    <row r="447" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A447">
         <v>162</v>
       </c>
@@ -8496,7 +8496,7 @@
         <v>177.71454560000001</v>
       </c>
     </row>
-    <row r="448" spans="1:5">
+    <row r="448" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A448">
         <v>163</v>
       </c>
@@ -8513,7 +8513,7 @@
         <v>197.1650377</v>
       </c>
     </row>
-    <row r="449" spans="1:5">
+    <row r="449" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A449">
         <v>164</v>
       </c>
@@ -8530,7 +8530,7 @@
         <v>204.01350690000001</v>
       </c>
     </row>
-    <row r="450" spans="1:5">
+    <row r="450" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A450">
         <v>165</v>
       </c>
@@ -8547,7 +8547,7 @@
         <v>234.3299796</v>
       </c>
     </row>
-    <row r="451" spans="1:5">
+    <row r="451" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A451">
         <v>156</v>
       </c>
@@ -8564,7 +8564,7 @@
         <v>280.05083009999998</v>
       </c>
     </row>
-    <row r="452" spans="1:5">
+    <row r="452" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A452">
         <v>157</v>
       </c>
@@ -8581,7 +8581,7 @@
         <v>280.98528879999998</v>
       </c>
     </row>
-    <row r="453" spans="1:5">
+    <row r="453" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A453">
         <v>166</v>
       </c>
@@ -8598,7 +8598,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="454" spans="1:5">
+    <row r="454" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A454">
         <v>169</v>
       </c>
@@ -8615,7 +8615,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="455" spans="1:5">
+    <row r="455" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A455">
         <v>170</v>
       </c>
@@ -8632,7 +8632,7 @@
         <v>129.5859221</v>
       </c>
     </row>
-    <row r="456" spans="1:5">
+    <row r="456" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A456">
         <v>171</v>
       </c>
@@ -8649,7 +8649,7 @@
         <v>136.26640080000001</v>
       </c>
     </row>
-    <row r="457" spans="1:5">
+    <row r="457" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A457">
         <v>172</v>
       </c>
@@ -8666,7 +8666,7 @@
         <v>155.75156849999999</v>
       </c>
     </row>
-    <row r="458" spans="1:5">
+    <row r="458" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A458">
         <v>173</v>
       </c>
@@ -8683,7 +8683,7 @@
         <v>184.62461440000001</v>
       </c>
     </row>
-    <row r="459" spans="1:5">
+    <row r="459" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A459">
         <v>174</v>
       </c>
@@ -8700,7 +8700,7 @@
         <v>205.17566099999999</v>
       </c>
     </row>
-    <row r="460" spans="1:5">
+    <row r="460" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A460">
         <v>175</v>
       </c>
@@ -8717,7 +8717,7 @@
         <v>233.42283040000001</v>
       </c>
     </row>
-    <row r="461" spans="1:5">
+    <row r="461" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A461">
         <v>176</v>
       </c>
@@ -8734,7 +8734,7 @@
         <v>247.76058269999999</v>
       </c>
     </row>
-    <row r="462" spans="1:5">
+    <row r="462" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A462">
         <v>167</v>
       </c>
@@ -8751,7 +8751,7 @@
         <v>266.52676689999998</v>
       </c>
     </row>
-    <row r="463" spans="1:5">
+    <row r="463" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A463">
         <v>168</v>
       </c>
@@ -8768,7 +8768,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="464" spans="1:5">
+    <row r="464" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A464">
         <v>177</v>
       </c>
@@ -8785,7 +8785,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="465" spans="1:5">
+    <row r="465" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A465">
         <v>180</v>
       </c>
@@ -8802,7 +8802,7 @@
         <v>101.69369260000001</v>
       </c>
     </row>
-    <row r="466" spans="1:5">
+    <row r="466" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A466">
         <v>181</v>
       </c>
@@ -8819,7 +8819,7 @@
         <v>123.7184414</v>
       </c>
     </row>
-    <row r="467" spans="1:5">
+    <row r="467" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A467">
         <v>182</v>
       </c>
@@ -8836,7 +8836,7 @@
         <v>165.7722431</v>
       </c>
     </row>
-    <row r="468" spans="1:5">
+    <row r="468" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A468">
         <v>183</v>
       </c>
@@ -8853,7 +8853,7 @@
         <v>175.01452879999999</v>
       </c>
     </row>
-    <row r="469" spans="1:5">
+    <row r="469" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A469">
         <v>184</v>
       </c>
@@ -8870,7 +8870,7 @@
         <v>193.43952100000001</v>
       </c>
     </row>
-    <row r="470" spans="1:5">
+    <row r="470" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A470">
         <v>185</v>
       </c>
@@ -8887,7 +8887,7 @@
         <v>207.44836040000001</v>
       </c>
     </row>
-    <row r="471" spans="1:5">
+    <row r="471" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A471">
         <v>186</v>
       </c>
@@ -8904,7 +8904,7 @@
         <v>207.3461034</v>
       </c>
     </row>
-    <row r="472" spans="1:5">
+    <row r="472" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A472">
         <v>187</v>
       </c>
@@ -8921,7 +8921,7 @@
         <v>222.79217840000001</v>
       </c>
     </row>
-    <row r="473" spans="1:5">
+    <row r="473" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A473">
         <v>178</v>
       </c>
@@ -8938,7 +8938,7 @@
         <v>257.8730339</v>
       </c>
     </row>
-    <row r="474" spans="1:5">
+    <row r="474" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A474">
         <v>179</v>
       </c>
@@ -8955,7 +8955,7 @@
         <v>272.02837620000003</v>
       </c>
     </row>
-    <row r="475" spans="1:5">
+    <row r="475" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A475">
         <v>188</v>
       </c>
@@ -8972,7 +8972,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="476" spans="1:5">
+    <row r="476" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A476">
         <v>191</v>
       </c>
@@ -8989,7 +8989,7 @@
         <v>81.291007329999999</v>
       </c>
     </row>
-    <row r="477" spans="1:5">
+    <row r="477" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A477">
         <v>192</v>
       </c>
@@ -9006,7 +9006,7 @@
         <v>115.8172273</v>
       </c>
     </row>
-    <row r="478" spans="1:5">
+    <row r="478" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A478">
         <v>193</v>
       </c>
@@ -9023,7 +9023,7 @@
         <v>136.0780188</v>
       </c>
     </row>
-    <row r="479" spans="1:5">
+    <row r="479" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A479">
         <v>194</v>
       </c>
@@ -9040,7 +9040,7 @@
         <v>177.63341159999999</v>
       </c>
     </row>
-    <row r="480" spans="1:5">
+    <row r="480" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A480">
         <v>195</v>
       </c>
@@ -9057,7 +9057,7 @@
         <v>196.80883370000001</v>
       </c>
     </row>
-    <row r="481" spans="1:5">
+    <row r="481" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A481">
         <v>196</v>
       </c>
@@ -9074,7 +9074,7 @@
         <v>201.5004045</v>
       </c>
     </row>
-    <row r="482" spans="1:5">
+    <row r="482" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A482">
         <v>197</v>
       </c>
@@ -9091,7 +9091,7 @@
         <v>209.11267760000001</v>
       </c>
     </row>
-    <row r="483" spans="1:5">
+    <row r="483" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A483">
         <v>198</v>
       </c>
@@ -9108,7 +9108,7 @@
         <v>219.95853149999999</v>
       </c>
     </row>
-    <row r="484" spans="1:5">
+    <row r="484" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A484">
         <v>189</v>
       </c>
@@ -9125,7 +9125,7 @@
         <v>217.09166999999999</v>
       </c>
     </row>
-    <row r="485" spans="1:5">
+    <row r="485" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A485">
         <v>190</v>
       </c>
@@ -9142,7 +9142,7 @@
         <v>277.78655629999997</v>
       </c>
     </row>
-    <row r="486" spans="1:5">
+    <row r="486" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A486">
         <v>199</v>
       </c>
@@ -9159,7 +9159,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="487" spans="1:5">
+    <row r="487" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A487">
         <v>202</v>
       </c>
@@ -9176,7 +9176,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="488" spans="1:5">
+    <row r="488" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A488">
         <v>203</v>
       </c>
@@ -9193,7 +9193,7 @@
         <v>113.753382</v>
       </c>
     </row>
-    <row r="489" spans="1:5">
+    <row r="489" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A489">
         <v>204</v>
       </c>
@@ -9210,7 +9210,7 @@
         <v>130.56338600000001</v>
       </c>
     </row>
-    <row r="490" spans="1:5">
+    <row r="490" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A490">
         <v>205</v>
       </c>
@@ -9227,7 +9227,7 @@
         <v>149.27155859999999</v>
       </c>
     </row>
-    <row r="491" spans="1:5">
+    <row r="491" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A491">
         <v>206</v>
       </c>
@@ -9244,7 +9244,7 @@
         <v>181.7080632</v>
       </c>
     </row>
-    <row r="492" spans="1:5">
+    <row r="492" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A492">
         <v>207</v>
       </c>
@@ -9261,7 +9261,7 @@
         <v>199.35870639999999</v>
       </c>
     </row>
-    <row r="493" spans="1:5">
+    <row r="493" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A493">
         <v>208</v>
       </c>
@@ -9278,7 +9278,7 @@
         <v>204.4977682</v>
       </c>
     </row>
-    <row r="494" spans="1:5">
+    <row r="494" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A494">
         <v>209</v>
       </c>
@@ -9295,7 +9295,7 @@
         <v>208.29329709999999</v>
       </c>
     </row>
-    <row r="495" spans="1:5">
+    <row r="495" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A495">
         <v>200</v>
       </c>
@@ -9312,7 +9312,7 @@
         <v>239.4890829</v>
       </c>
     </row>
-    <row r="496" spans="1:5">
+    <row r="496" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A496">
         <v>201</v>
       </c>
@@ -9329,7 +9329,7 @@
         <v>248.84211289999999</v>
       </c>
     </row>
-    <row r="497" spans="1:5">
+    <row r="497" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A497">
         <v>210</v>
       </c>
@@ -9346,7 +9346,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="498" spans="1:5">
+    <row r="498" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A498">
         <v>213</v>
       </c>
@@ -9363,7 +9363,7 @@
         <v>83.75425817</v>
       </c>
     </row>
-    <row r="499" spans="1:5">
+    <row r="499" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A499">
         <v>214</v>
       </c>
@@ -9380,7 +9380,7 @@
         <v>123.0290004</v>
       </c>
     </row>
-    <row r="500" spans="1:5">
+    <row r="500" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A500">
         <v>215</v>
       </c>
@@ -9397,7 +9397,7 @@
         <v>143.7465468</v>
       </c>
     </row>
-    <row r="501" spans="1:5">
+    <row r="501" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A501">
         <v>216</v>
       </c>
@@ -9414,7 +9414,7 @@
         <v>160.11791020000001</v>
       </c>
     </row>
-    <row r="502" spans="1:5">
+    <row r="502" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A502">
         <v>217</v>
       </c>
@@ -9431,7 +9431,7 @@
         <v>183.46297939999999</v>
       </c>
     </row>
-    <row r="503" spans="1:5">
+    <row r="503" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A503">
         <v>218</v>
       </c>
@@ -9448,7 +9448,7 @@
         <v>200.5918743</v>
       </c>
     </row>
-    <row r="504" spans="1:5">
+    <row r="504" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A504">
         <v>219</v>
       </c>
@@ -9465,7 +9465,7 @@
         <v>210.15571829999999</v>
       </c>
     </row>
-    <row r="505" spans="1:5">
+    <row r="505" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A505">
         <v>220</v>
       </c>
@@ -9482,7 +9482,7 @@
         <v>212.40000319999999</v>
       </c>
     </row>
-    <row r="506" spans="1:5">
+    <row r="506" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A506">
         <v>211</v>
       </c>
@@ -9499,7 +9499,7 @@
         <v>227.03573639999999</v>
       </c>
     </row>
-    <row r="507" spans="1:5">
+    <row r="507" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A507">
         <v>212</v>
       </c>
@@ -9516,7 +9516,7 @@
         <v>252.75781029999999</v>
       </c>
     </row>
-    <row r="508" spans="1:5">
+    <row r="508" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A508">
         <v>221</v>
       </c>
@@ -9533,7 +9533,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="509" spans="1:5">
+    <row r="509" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A509">
         <v>224</v>
       </c>
@@ -9550,7 +9550,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="510" spans="1:5">
+    <row r="510" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A510">
         <v>225</v>
       </c>
@@ -9567,7 +9567,7 @@
         <v>117.0688342</v>
       </c>
     </row>
-    <row r="511" spans="1:5">
+    <row r="511" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A511">
         <v>226</v>
       </c>
@@ -9584,7 +9584,7 @@
         <v>136.16731590000001</v>
       </c>
     </row>
-    <row r="512" spans="1:5">
+    <row r="512" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A512">
         <v>227</v>
       </c>
@@ -9601,7 +9601,7 @@
         <v>161.20375770000001</v>
       </c>
     </row>
-    <row r="513" spans="1:5">
+    <row r="513" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A513">
         <v>228</v>
       </c>
@@ -9618,7 +9618,7 @@
         <v>174.25470250000001</v>
       </c>
     </row>
-    <row r="514" spans="1:5">
+    <row r="514" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A514">
         <v>229</v>
       </c>
@@ -9635,7 +9635,7 @@
         <v>201.546412</v>
       </c>
     </row>
-    <row r="515" spans="1:5">
+    <row r="515" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A515">
         <v>230</v>
       </c>
@@ -9652,7 +9652,7 @@
         <v>208.8539007</v>
       </c>
     </row>
-    <row r="516" spans="1:5">
+    <row r="516" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A516">
         <v>231</v>
       </c>
@@ -9669,7 +9669,7 @@
         <v>235.22971050000001</v>
       </c>
     </row>
-    <row r="517" spans="1:5">
+    <row r="517" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A517">
         <v>222</v>
       </c>
@@ -9686,7 +9686,7 @@
         <v>237.41778679999999</v>
       </c>
     </row>
-    <row r="518" spans="1:5">
+    <row r="518" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A518">
         <v>223</v>
       </c>
@@ -9703,7 +9703,7 @@
         <v>216.0012854</v>
       </c>
     </row>
-    <row r="519" spans="1:5">
+    <row r="519" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A519">
         <v>232</v>
       </c>
@@ -9720,7 +9720,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="520" spans="1:5">
+    <row r="520" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A520">
         <v>235</v>
       </c>
@@ -9737,7 +9737,7 @@
         <v>86.051808699999995</v>
       </c>
     </row>
-    <row r="521" spans="1:5">
+    <row r="521" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A521">
         <v>236</v>
       </c>
@@ -9754,7 +9754,7 @@
         <v>143.8707173</v>
       </c>
     </row>
-    <row r="522" spans="1:5">
+    <row r="522" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A522">
         <v>237</v>
       </c>
@@ -9771,7 +9771,7 @@
         <v>154.8919827</v>
       </c>
     </row>
-    <row r="523" spans="1:5">
+    <row r="523" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A523">
         <v>238</v>
       </c>
@@ -9788,7 +9788,7 @@
         <v>172.8749751</v>
       </c>
     </row>
-    <row r="524" spans="1:5">
+    <row r="524" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A524">
         <v>239</v>
       </c>
@@ -9805,7 +9805,7 @@
         <v>186.33386870000001</v>
       </c>
     </row>
-    <row r="525" spans="1:5">
+    <row r="525" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A525">
         <v>240</v>
       </c>
@@ -9822,7 +9822,7 @@
         <v>197.72340439999999</v>
       </c>
     </row>
-    <row r="526" spans="1:5">
+    <row r="526" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A526">
         <v>241</v>
       </c>
@@ -9839,7 +9839,7 @@
         <v>212.84409239999999</v>
       </c>
     </row>
-    <row r="527" spans="1:5">
+    <row r="527" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A527">
         <v>242</v>
       </c>
@@ -9856,7 +9856,7 @@
         <v>235.1492634</v>
       </c>
     </row>
-    <row r="528" spans="1:5">
+    <row r="528" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A528">
         <v>233</v>
       </c>
@@ -9873,7 +9873,7 @@
         <v>227.63945419999999</v>
       </c>
     </row>
-    <row r="529" spans="1:5">
+    <row r="529" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A529">
         <v>234</v>
       </c>
@@ -9890,7 +9890,7 @@
         <v>306.15682040000002</v>
       </c>
     </row>
-    <row r="530" spans="1:5">
+    <row r="530" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A530">
         <v>243</v>
       </c>
@@ -9907,7 +9907,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="531" spans="1:5">
+    <row r="531" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A531">
         <v>246</v>
       </c>
@@ -9924,7 +9924,7 @@
         <v>83.768227359999997</v>
       </c>
     </row>
-    <row r="532" spans="1:5">
+    <row r="532" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A532">
         <v>247</v>
       </c>
@@ -9941,7 +9941,7 @@
         <v>108.3414391</v>
       </c>
     </row>
-    <row r="533" spans="1:5">
+    <row r="533" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A533">
         <v>248</v>
       </c>
@@ -9958,7 +9958,7 @@
         <v>137.07811219999999</v>
       </c>
     </row>
-    <row r="534" spans="1:5">
+    <row r="534" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A534">
         <v>249</v>
       </c>
@@ -9975,7 +9975,7 @@
         <v>178.61408230000001</v>
       </c>
     </row>
-    <row r="535" spans="1:5">
+    <row r="535" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A535">
         <v>250</v>
       </c>
@@ -9992,7 +9992,7 @@
         <v>201.5951556</v>
       </c>
     </row>
-    <row r="536" spans="1:5">
+    <row r="536" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A536">
         <v>251</v>
       </c>
@@ -10009,7 +10009,7 @@
         <v>213.904776</v>
       </c>
     </row>
-    <row r="537" spans="1:5">
+    <row r="537" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A537">
         <v>252</v>
       </c>
@@ -10026,7 +10026,7 @@
         <v>226.9437997</v>
       </c>
     </row>
-    <row r="538" spans="1:5">
+    <row r="538" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A538">
         <v>253</v>
       </c>
@@ -10043,7 +10043,7 @@
         <v>253.330365</v>
       </c>
     </row>
-    <row r="539" spans="1:5">
+    <row r="539" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A539">
         <v>244</v>
       </c>
@@ -10060,7 +10060,7 @@
         <v>236.41919770000001</v>
       </c>
     </row>
-    <row r="540" spans="1:5">
+    <row r="540" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A540">
         <v>245</v>
       </c>
@@ -10077,7 +10077,7 @@
         <v>279.60967909999999</v>
       </c>
     </row>
-    <row r="541" spans="1:5">
+    <row r="541" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A541">
         <v>254</v>
       </c>
@@ -10094,7 +10094,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="542" spans="1:5">
+    <row r="542" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A542">
         <v>257</v>
       </c>
@@ -10111,7 +10111,7 @@
         <v>76.188751420000003</v>
       </c>
     </row>
-    <row r="543" spans="1:5">
+    <row r="543" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A543">
         <v>258</v>
       </c>
@@ -10128,7 +10128,7 @@
         <v>118.4241569</v>
       </c>
     </row>
-    <row r="544" spans="1:5">
+    <row r="544" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A544">
         <v>259</v>
       </c>
@@ -10145,7 +10145,7 @@
         <v>136.6728196</v>
       </c>
     </row>
-    <row r="545" spans="1:5">
+    <row r="545" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A545">
         <v>260</v>
       </c>
@@ -10162,7 +10162,7 @@
         <v>171.9279794</v>
       </c>
     </row>
-    <row r="546" spans="1:5">
+    <row r="546" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A546">
         <v>261</v>
       </c>
@@ -10179,7 +10179,7 @@
         <v>191.53310629999999</v>
       </c>
     </row>
-    <row r="547" spans="1:5">
+    <row r="547" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A547">
         <v>262</v>
       </c>
@@ -10196,7 +10196,7 @@
         <v>213.60647950000001</v>
       </c>
     </row>
-    <row r="548" spans="1:5">
+    <row r="548" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A548">
         <v>263</v>
       </c>
@@ -10213,7 +10213,7 @@
         <v>223.30099269999999</v>
       </c>
     </row>
-    <row r="549" spans="1:5">
+    <row r="549" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A549">
         <v>264</v>
       </c>
@@ -10230,7 +10230,7 @@
         <v>232.72759669999999</v>
       </c>
     </row>
-    <row r="550" spans="1:5">
+    <row r="550" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A550">
         <v>255</v>
       </c>
@@ -10247,7 +10247,7 @@
         <v>264.05065999999999</v>
       </c>
     </row>
-    <row r="551" spans="1:5">
+    <row r="551" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A551">
         <v>256</v>
       </c>
@@ -10264,7 +10264,7 @@
         <v>252.6585575</v>
       </c>
     </row>
-    <row r="552" spans="1:5">
+    <row r="552" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A552">
         <v>265</v>
       </c>
@@ -10281,7 +10281,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="553" spans="1:5">
+    <row r="553" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A553">
         <v>268</v>
       </c>
@@ -10298,7 +10298,7 @@
         <v>68.795162379999994</v>
       </c>
     </row>
-    <row r="554" spans="1:5">
+    <row r="554" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A554">
         <v>269</v>
       </c>
@@ -10315,7 +10315,7 @@
         <v>140.05206240000001</v>
       </c>
     </row>
-    <row r="555" spans="1:5">
+    <row r="555" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A555">
         <v>270</v>
       </c>
@@ -10332,7 +10332,7 @@
         <v>154.2088541</v>
       </c>
     </row>
-    <row r="556" spans="1:5">
+    <row r="556" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A556">
         <v>271</v>
       </c>
@@ -10349,7 +10349,7 @@
         <v>163.02983409999999</v>
       </c>
     </row>
-    <row r="557" spans="1:5">
+    <row r="557" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A557">
         <v>272</v>
       </c>
@@ -10366,7 +10366,7 @@
         <v>188.86671050000001</v>
       </c>
     </row>
-    <row r="558" spans="1:5">
+    <row r="558" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A558">
         <v>273</v>
       </c>
@@ -10383,7 +10383,7 @@
         <v>195.6432154</v>
       </c>
     </row>
-    <row r="559" spans="1:5">
+    <row r="559" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A559">
         <v>274</v>
       </c>
@@ -10400,7 +10400,7 @@
         <v>211.7062339</v>
       </c>
     </row>
-    <row r="560" spans="1:5">
+    <row r="560" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A560">
         <v>275</v>
       </c>
@@ -10417,7 +10417,7 @@
         <v>237.5819477</v>
       </c>
     </row>
-    <row r="561" spans="1:5">
+    <row r="561" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A561">
         <v>266</v>
       </c>
@@ -10434,7 +10434,7 @@
         <v>251.70449479999999</v>
       </c>
     </row>
-    <row r="562" spans="1:5">
+    <row r="562" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A562">
         <v>267</v>
       </c>
@@ -10451,7 +10451,7 @@
         <v>268.13738749999999</v>
       </c>
     </row>
-    <row r="563" spans="1:5">
+    <row r="563" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A563">
         <v>276</v>
       </c>
@@ -10468,7 +10468,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="564" spans="1:5">
+    <row r="564" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A564">
         <v>279</v>
       </c>
@@ -10485,7 +10485,7 @@
         <v>85.449320299999997</v>
       </c>
     </row>
-    <row r="565" spans="1:5">
+    <row r="565" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A565">
         <v>280</v>
       </c>
@@ -10502,7 +10502,7 @@
         <v>151.4227922</v>
       </c>
     </row>
-    <row r="566" spans="1:5">
+    <row r="566" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A566">
         <v>281</v>
       </c>
@@ -10519,7 +10519,7 @@
         <v>165.47001119999999</v>
       </c>
     </row>
-    <row r="567" spans="1:5">
+    <row r="567" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A567">
         <v>282</v>
       </c>
@@ -10536,7 +10536,7 @@
         <v>174.9497179</v>
       </c>
     </row>
-    <row r="568" spans="1:5">
+    <row r="568" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A568">
         <v>283</v>
       </c>
@@ -10553,7 +10553,7 @@
         <v>183.6575325</v>
       </c>
     </row>
-    <row r="569" spans="1:5">
+    <row r="569" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A569">
         <v>284</v>
       </c>
@@ -10570,7 +10570,7 @@
         <v>202.1287561</v>
       </c>
     </row>
-    <row r="570" spans="1:5">
+    <row r="570" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A570">
         <v>285</v>
       </c>
@@ -10587,7 +10587,7 @@
         <v>217.81257669999999</v>
       </c>
     </row>
-    <row r="571" spans="1:5">
+    <row r="571" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A571">
         <v>286</v>
       </c>
@@ -10604,7 +10604,7 @@
         <v>217.92566590000001</v>
       </c>
     </row>
-    <row r="572" spans="1:5">
+    <row r="572" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A572">
         <v>277</v>
       </c>
@@ -10621,7 +10621,7 @@
         <v>198.06127090000001</v>
       </c>
     </row>
-    <row r="573" spans="1:5">
+    <row r="573" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A573">
         <v>278</v>
       </c>
